--- a/courses/Micro-And-Macro-Economics/projects/perfect-competition-marginal-costs/farm-profit-optimizer-key.xlsx
+++ b/courses/Micro-And-Macro-Economics/projects/perfect-competition-marginal-costs/farm-profit-optimizer-key.xlsx
@@ -474,7 +474,7 @@
     <numFmt numFmtId="167" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,82 +537,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF0070C0"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF4F6228"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFC00000"/>
-      <name val="Arial"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="15">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -651,49 +577,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B5E40"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDE9D9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,7 +606,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -762,74 +658,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf applyFont="1" numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf applyFill="1" numFmtId="1" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="164" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="165" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf applyFill="1" numFmtId="166" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="167" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="2" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="10" fontId="11" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf applyFill="1" numFmtId="2" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="12" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf applyFill="1" numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1"/>
-    <xf applyFill="1" numFmtId="1" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="164" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="1" fontId="16" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="164" fontId="16" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="165" fontId="16" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="2" fontId="12" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="164" fontId="8" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" applyFont="1" numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf applyFill="1" numFmtId="6" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="165" fontId="18" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="2" fontId="18" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="164" fontId="18" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1"/>
-    <xf applyFill="1" numFmtId="168" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf applyFill="1" numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="11" fillId="14" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf applyFill="1" numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3298,7 +3126,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:B37"/>
+  <dimension ref="B2:B32"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="110" customWidth="1"/>
@@ -3325,10 +3153,8 @@
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Read the assumptions on the Model sheet. Cell colours follow the house legend at the bottom of this sheet: tan = hardcoded input you may change, blue-on-grey = formula (do not overtype), yellow = key assumption, gold = the Solver objective, light red = a Solver constraint.</t>
-        </is>
+      <c r="B8" s="3" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="25" x14ac:dyDescent="0.35">
@@ -3376,110 +3202,63 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="2:2">
-      <c r="B20" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">COLOR CODING LEGEND  —  the house convention (see WORKBOOK-STANDARDS.md)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" spans="2:2">
-      <c r="B21" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Input — hardcoded:  black text on tan.  A number typed in, not calculated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" spans="2:2">
-      <c r="B22" s="73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Formula — calculated:  blue text on light grey.  Derived from cells on this sheet. Never type over it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" spans="2:2">
-      <c r="B23" s="74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link — another sheet:  olive text on light grey.  Pulls a value from another sheet in this workbook.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" spans="2:2">
-      <c r="B24" s="75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">External source:  red text.  A live reference to another file. Avoided here — external figures are typed in as tan hardcodes with a source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" spans="2:2">
-      <c r="B25" s="76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Warning / caveat:  bold dark red.  Something the model cannot do, or a basis inconsistency to state out loud.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" spans="2:2">
-      <c r="B26" s="77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Source note:  grey italic, 9pt.  Provenance, vintage, or method commentary — not part of the calculation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" spans="2:2">
-      <c r="B27" s="71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Header:  white bold on dark green.  Column or table header row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Key assumption:  black text on yellow.  A FITTED or judgmental input rather than an observed one — the first thing to challenge.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solver objective:  gold fill.  The cell Solver optimizes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Solver constraint:  light red fill.  Cells Solver is constrained to (caps and limits named in the Solver model).</t>
-        </is>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B21" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B23" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B24" s="30" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B25" s="34" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B27" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" ht="25" x14ac:dyDescent="0.35">
+      <c r="B28" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" ht="25" x14ac:dyDescent="0.35">
+      <c r="B29" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B32" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" ht="25" x14ac:dyDescent="0.35">
-      <c r="B33" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" ht="25" x14ac:dyDescent="0.35">
-      <c r="B34" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B35" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B36" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B37" s="3" t="s">
+      <c r="B32" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -3506,19 +3285,19 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="9">
         <v>36</v>
       </c>
     </row>
@@ -3526,7 +3305,7 @@
       <c r="B6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="42">
+      <c r="C6" s="10">
         <v>20000</v>
       </c>
     </row>
@@ -3534,7 +3313,7 @@
       <c r="B7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="9">
         <v>40</v>
       </c>
     </row>
@@ -3542,25 +3321,25 @@
       <c r="B8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="11">
         <f>season_wks*labor_hrs_week</f>
         <v>1440</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="12" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3568,17 +3347,17 @@
       <c r="B11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="10">
         <v>50000</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="13">
         <v>0.5</v>
       </c>
-      <c r="E11" s="46">
+      <c r="E11" s="14">
         <f>C11/labor_hrs_season</f>
         <v>34.722222222222221</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="11">
         <f>labor_hrs_season*D11</f>
         <v>720</v>
       </c>
@@ -3587,30 +3366,30 @@
       <c r="B12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="10">
         <v>25000</v>
       </c>
-      <c r="D12" s="45">
+      <c r="D12" s="13">
         <v>1</v>
       </c>
-      <c r="E12" s="46">
+      <c r="E12" s="14">
         <f>C12/labor_hrs_season</f>
         <v>17.361111111111111</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="11">
         <f>labor_hrs_season*D12</f>
         <v>1440</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="47" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="47" t="s">
+      <c r="E14" s="28" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3618,7 +3397,7 @@
       <c r="B15" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="33">
         <v>64</v>
       </c>
       <c r="D15" s="35" t="s">
@@ -3632,7 +3411,7 @@
       <c r="B16" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="33">
         <v>4</v>
       </c>
       <c r="D16" s="35" t="s">
@@ -3643,32 +3422,32 @@
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B18" s="39" t="s">
+      <c r="B18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="40"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="2:8" ht="26" x14ac:dyDescent="0.35">
-      <c r="B19" s="49" t="s">
+      <c r="B19" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="49" t="s">
+      <c r="E19" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="F19" s="49" t="s">
+      <c r="F19" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="G19" s="49" t="s">
+      <c r="G19" s="15" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3676,22 +3455,22 @@
       <c r="B20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="41">
+      <c r="C20" s="9">
         <v>20</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="10">
         <v>8800</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="16">
         <v>2.5</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="10">
         <v>880</v>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="17">
         <v>0.1</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="8" t="s">
         <v>48</v>
       </c>
     </row>
@@ -3699,20 +3478,20 @@
       <c r="B21" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="9">
         <v>20</v>
       </c>
-      <c r="D21" s="42">
+      <c r="D21" s="10">
         <v>2094</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="18">
         <f>E20/3</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="F21" s="42">
+      <c r="F21" s="10">
         <v>440</v>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="17">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -3720,48 +3499,48 @@
       <c r="B22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="9">
         <v>30</v>
       </c>
-      <c r="D22" s="42">
+      <c r="D22" s="10">
         <v>2700</v>
       </c>
-      <c r="E22" s="53">
+      <c r="E22" s="18">
         <f>E20/2</f>
         <v>1.25</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F22" s="10">
         <v>880</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="17">
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="47" t="s">
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="47" t="s">
+      <c r="G24" s="28" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B25" s="44" t="s">
+      <c r="B25" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C25" s="44" t="s">
+      <c r="C25" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E25" s="44" t="s">
+      <c r="E25" s="12" t="s">
         <v>54</v>
       </c>
       <c r="F25" s="36"/>
@@ -3771,14 +3550,14 @@
       <c r="B26" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="54">
+      <c r="C26" s="19">
         <v>10.004048672116639</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="37">
         <f>max_tomato</f>
         <v>20</v>
       </c>
-      <c r="E26" s="56" t="str">
+      <c r="E26" s="8" t="str">
         <f>IF(C26&gt;max_tomato,"OVER MAX","ok")</f>
         <v>ok</v>
       </c>
@@ -3793,14 +3572,14 @@
       <c r="B27" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C27" s="54">
+      <c r="C27" s="19">
         <v>20</v>
       </c>
-      <c r="D27" s="55">
+      <c r="D27" s="37">
         <f>max_carrot</f>
         <v>20</v>
       </c>
-      <c r="E27" s="56" t="str">
+      <c r="E27" s="8" t="str">
         <f>IF(C27&gt;max_carrot,"OVER MAX","ok")</f>
         <v>ok</v>
       </c>
@@ -3815,14 +3594,14 @@
       <c r="B28" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="54">
+      <c r="C28" s="19">
         <v>30</v>
       </c>
-      <c r="D28" s="55">
+      <c r="D28" s="37">
         <f>max_mesclun</f>
         <v>30</v>
       </c>
-      <c r="E28" s="56" t="str">
+      <c r="E28" s="8" t="str">
         <f>IF(C28&gt;max_mesclun,"OVER MAX","ok")</f>
         <v>ok</v>
       </c>
@@ -3834,36 +3613,36 @@
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B31" s="44" t="s">
+      <c r="B31" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="44" t="s">
+      <c r="C31" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="D31" s="44" t="s">
+      <c r="D31" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="E31" s="44" t="s">
+      <c r="E31" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="44" t="s">
+      <c r="F31" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="G31" s="44" t="s">
+      <c r="G31" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="H31" s="44" t="s">
+      <c r="H31" s="12" t="s">
         <v>60</v>
       </c>
     </row>
@@ -3871,27 +3650,27 @@
       <c r="B32" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="57">
+      <c r="C32" s="20">
         <f>q_tomato</f>
         <v>10.004048672116639</v>
       </c>
-      <c r="D32" s="58">
+      <c r="D32" s="21">
         <f>q_tomato*price_tomato</f>
         <v>88035.628314626418</v>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="11">
         <f>q_tomato*laborwk_tomato*season_wks*(1+dim_tomato)^q_tomato</f>
         <v>2336.2146470583803</v>
       </c>
-      <c r="F32" s="58">
+      <c r="F32" s="21">
         <f>IF(hrs_total=0,0,E32*labor_cost_total/hrs_total)</f>
         <v>46091.075416069114</v>
       </c>
-      <c r="G32" s="58">
+      <c r="G32" s="21">
         <f>q_tomato*fert_tomato</f>
         <v>8803.5628314626429</v>
       </c>
-      <c r="H32" s="58">
+      <c r="H32" s="21">
         <f>F32+G32</f>
         <v>54894.638247531759</v>
       </c>
@@ -3900,27 +3679,27 @@
       <c r="B33" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="57">
+      <c r="C33" s="20">
         <f>q_carrot</f>
         <v>20</v>
       </c>
-      <c r="D33" s="58">
+      <c r="D33" s="21">
         <f>q_carrot*price_carrot</f>
         <v>41880</v>
       </c>
-      <c r="E33" s="43">
+      <c r="E33" s="11">
         <f>q_carrot*laborwk_carrot*season_wks*(1+dim_carrot)^q_carrot</f>
         <v>983.16986417423732</v>
       </c>
-      <c r="F33" s="58">
+      <c r="F33" s="21">
         <f>IF(hrs_total=0,0,E33*labor_cost_total/hrs_total)</f>
         <v>19396.914754181322</v>
       </c>
-      <c r="G33" s="58">
+      <c r="G33" s="21">
         <f>q_carrot*fert_carrot</f>
         <v>8800</v>
       </c>
-      <c r="H33" s="58">
+      <c r="H33" s="21">
         <f>F33+G33</f>
         <v>28196.914754181322</v>
       </c>
@@ -3929,27 +3708,27 @@
       <c r="B34" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="57">
+      <c r="C34" s="20">
         <f>q_mesclun</f>
         <v>30</v>
       </c>
-      <c r="D34" s="58">
+      <c r="D34" s="21">
         <f>q_mesclun*price_mesclun</f>
         <v>81000</v>
       </c>
-      <c r="E34" s="43">
+      <c r="E34" s="11">
         <f>q_mesclun*laborwk_mesclun*season_wks*(1+dim_mesclun)^q_mesclun</f>
         <v>1959.6780360096488</v>
       </c>
-      <c r="F34" s="58">
+      <c r="F34" s="21">
         <f>IF(hrs_total=0,0,E34*labor_cost_total/hrs_total)</f>
         <v>38662.401274927804</v>
       </c>
-      <c r="G34" s="58">
+      <c r="G34" s="21">
         <f>q_mesclun*fert_mesclun</f>
         <v>26400</v>
       </c>
-      <c r="H34" s="58">
+      <c r="H34" s="21">
         <f>F34+G34</f>
         <v>65062.401274927804</v>
       </c>
@@ -3958,43 +3737,43 @@
       <c r="B35" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="C35" s="59">
+      <c r="C35" s="23">
         <f>SUM(C32:C34)</f>
         <v>60.004048672116639</v>
       </c>
-      <c r="D35" s="60">
+      <c r="D35" s="24">
         <f>SUM(D32:D34)</f>
         <v>210915.6283146264</v>
       </c>
-      <c r="E35" s="61">
+      <c r="E35" s="25">
         <f>SUM(E32:E34)</f>
         <v>5279.0625472422662</v>
       </c>
-      <c r="F35" s="60">
+      <c r="F35" s="24">
         <f>labor_cost_total</f>
         <v>104150.39144517823</v>
       </c>
-      <c r="G35" s="60">
+      <c r="G35" s="24">
         <f>SUM(G32:G34)</f>
         <v>44003.562831462645</v>
       </c>
-      <c r="H35" s="60">
+      <c r="H35" s="24">
         <f>SUM(H32:H34)</f>
         <v>148153.9542766409</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C37" s="40"/>
-      <c r="D37" s="40"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B38" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C38" s="43">
+      <c r="C38" s="11">
         <f>MIN(perm_field_hrs,hrs_total)</f>
         <v>720</v>
       </c>
@@ -4003,7 +3782,7 @@
       <c r="B39" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="C39" s="43">
+      <c r="C39" s="11">
         <f>hrs_total-perm_used</f>
         <v>4559.0625472422662</v>
       </c>
@@ -4012,11 +3791,11 @@
       <c r="B40" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="62">
+      <c r="C40" s="18">
         <f>temp_hrs/temp_hrs_each</f>
         <v>3.1660156578071295</v>
       </c>
-      <c r="D40" s="56" t="str">
+      <c r="D40" s="8" t="str">
         <f>IF(temp_needed&gt;temp_max,"INFEASIBLE — exceeds temp max","ok")</f>
         <v>ok</v>
       </c>
@@ -4025,20 +3804,20 @@
       <c r="B41" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="C41" s="58">
+      <c r="C41" s="21">
         <f>perm_used*wage_perm+temp_hrs*wage_temp</f>
         <v>104150.39144517823</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C43" s="40"/>
-      <c r="D43" s="47" t="s">
+      <c r="C43" s="7"/>
+      <c r="D43" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="E43" s="47" t="s">
+      <c r="E43" s="28" t="s">
         <v>102</v>
       </c>
     </row>
@@ -4046,7 +3825,7 @@
       <c r="B44" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="63">
+      <c r="C44" s="38">
         <f>rev_total</f>
         <v>210915.6283146264</v>
       </c>
@@ -4055,7 +3834,7 @@
       <c r="B45" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="63">
+      <c r="C45" s="38">
         <f>H35</f>
         <v>148153.9542766409</v>
       </c>
@@ -4064,7 +3843,7 @@
       <c r="B46" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C46" s="63">
+      <c r="C46" s="38">
         <f>costs_fixed</f>
         <v>20000</v>
       </c>
@@ -4073,7 +3852,7 @@
       <c r="B47" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C47" s="63">
+      <c r="C47" s="38">
         <f>C45+C46</f>
         <v>168153.9542766409</v>
       </c>
@@ -4086,10 +3865,10 @@
         <f>rev_total-costs_total</f>
         <v>42761.674037985504</v>
       </c>
-      <c r="D48" s="64" t="s">
+      <c r="D48" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="E48" s="64" t="s">
+      <c r="E48" s="29" t="s">
         <v>103</v>
       </c>
     </row>
@@ -4097,23 +3876,23 @@
       <c r="B49" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="56" t="str">
+      <c r="C49" s="8" t="str">
         <f>IF(beds_total&gt;beds_max,"OVER 64 BEDS","ok")</f>
         <v>ok</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B51" s="39" t="s">
+      <c r="B51" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B52" s="22" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="52" t="s">
+      <c r="C52" s="8" t="s">
         <v>75</v>
       </c>
     </row>
@@ -4121,7 +3900,7 @@
       <c r="B53" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="65">
+      <c r="C53" s="27">
         <v>42762</v>
       </c>
     </row>
@@ -4129,7 +3908,7 @@
       <c r="B54" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="C54" s="52" t="s">
+      <c r="C54" s="8" t="s">
         <v>77</v>
       </c>
     </row>
@@ -4137,7 +3916,7 @@
       <c r="B55" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="C55" s="52" t="s">
+      <c r="C55" s="8" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4145,7 +3924,7 @@
       <c r="B56" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="C56" s="52" t="s">
+      <c r="C56" s="8" t="s">
         <v>81</v>
       </c>
     </row>
@@ -4153,7 +3932,7 @@
       <c r="B57" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C57" s="52" t="s">
+      <c r="C57" s="8" t="s">
         <v>83</v>
       </c>
     </row>
@@ -4188,4589 +3967,4589 @@
       </c>
     </row>
     <row r="4" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="40"/>
-      <c r="F4" s="40"/>
-      <c r="G4" s="40"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="40"/>
-      <c r="K4" s="40"/>
-      <c r="L4" s="40"/>
-      <c r="M4" s="40"/>
-      <c r="N4" s="40"/>
-      <c r="O4" s="40"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="I5" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="M5" s="44" t="s">
+      <c r="M5" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="N5" s="44" t="s">
+      <c r="N5" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="O5" s="44" t="s">
+      <c r="O5" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="P5" s="44" t="s">
+      <c r="P5" s="12" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B6" s="41">
-        <v>0</v>
-      </c>
-      <c r="C6" s="66">
+      <c r="B6" s="20">
+        <v>0</v>
+      </c>
+      <c r="C6" s="11">
         <f t="shared" ref="C6:C26" si="0">B6*laborwk_tomato*season_wks*(1+dim_tomato)^B6</f>
         <v>0</v>
       </c>
-      <c r="D6" s="66">
+      <c r="D6" s="11">
         <f t="shared" ref="D6:D26" si="1">MIN(perm_field_hrs,C6)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="11">
         <f t="shared" ref="E6:E26" si="2">C6-D6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="67">
+      <c r="F6" s="18">
         <f t="shared" ref="F6:F26" si="3">E6/temp_hrs_each</f>
         <v>0</v>
       </c>
-      <c r="G6" s="68">
+      <c r="G6" s="21">
         <f t="shared" ref="G6:G26" si="4">D6*wage_perm+E6*wage_temp</f>
         <v>0</v>
       </c>
-      <c r="H6" s="68">
+      <c r="H6" s="21">
         <f t="shared" ref="H6:H26" si="5">B6*fert_tomato</f>
         <v>0</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="21">
         <f t="shared" ref="I6:I26" si="6">G6+H6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="68">
+      <c r="J6" s="21">
         <f t="shared" ref="J6:J26" si="7">I6+costs_fixed</f>
         <v>20000</v>
       </c>
-      <c r="M6" s="68">
+      <c r="M6" s="21">
         <f t="shared" ref="M6:M26" si="8">B6*price_tomato-J6</f>
         <v>-20000</v>
       </c>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B7" s="41">
+      <c r="B7" s="20">
         <v>1</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="11">
         <f t="shared" si="0"/>
         <v>99.000000000000014</v>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="11">
         <f t="shared" si="1"/>
         <v>99.000000000000014</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F7" s="53">
+      <c r="F7" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="21">
         <f t="shared" si="4"/>
         <v>3437.5000000000005</v>
       </c>
-      <c r="H7" s="58">
+      <c r="H7" s="21">
         <f t="shared" si="5"/>
         <v>880</v>
       </c>
-      <c r="I7" s="58">
+      <c r="I7" s="21">
         <f t="shared" si="6"/>
         <v>4317.5</v>
       </c>
-      <c r="J7" s="58">
+      <c r="J7" s="21">
         <f t="shared" si="7"/>
         <v>24317.5</v>
       </c>
-      <c r="K7" s="58">
+      <c r="K7" s="21">
         <f t="shared" ref="K7:K26" si="9">J7-J6</f>
         <v>4317.5</v>
       </c>
-      <c r="L7" s="58">
+      <c r="L7" s="21">
         <f t="shared" ref="L7:L26" si="10">I7/B7</f>
         <v>4317.5</v>
       </c>
-      <c r="M7" s="58">
+      <c r="M7" s="21">
         <f t="shared" si="8"/>
         <v>-15517.5</v>
       </c>
-      <c r="N7" s="69" t="str">
+      <c r="N7" s="8" t="str">
         <f t="shared" ref="N7:N25" si="11">IF(F7&gt;temp_max,"INFEASIBLE",IF(AND(price_tomato&gt;K7,price_tomato&lt;K8),"&lt;-- P ~ MC",""))</f>
         <v/>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="26">
         <f t="shared" ref="O7:O26" si="12">(B7+B6)/2</f>
         <v>0.5</v>
       </c>
-      <c r="P7" s="68">
+      <c r="P7" s="21">
         <f t="shared" ref="P7:P26" si="13">price_tomato</f>
         <v>8800</v>
       </c>
     </row>
     <row r="8" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B8" s="41">
+      <c r="B8" s="20">
         <v>2</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="11">
         <f t="shared" si="0"/>
         <v>217.80000000000004</v>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="11">
         <f t="shared" si="1"/>
         <v>217.80000000000004</v>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F8" s="53">
+      <c r="F8" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G8" s="58">
+      <c r="G8" s="21">
         <f t="shared" si="4"/>
         <v>7562.5000000000009</v>
       </c>
-      <c r="H8" s="58">
+      <c r="H8" s="21">
         <f t="shared" si="5"/>
         <v>1760</v>
       </c>
-      <c r="I8" s="58">
+      <c r="I8" s="21">
         <f t="shared" si="6"/>
         <v>9322.5</v>
       </c>
-      <c r="J8" s="58">
+      <c r="J8" s="21">
         <f t="shared" si="7"/>
         <v>29322.5</v>
       </c>
-      <c r="K8" s="58">
+      <c r="K8" s="21">
         <f t="shared" si="9"/>
         <v>5005</v>
       </c>
-      <c r="L8" s="58">
+      <c r="L8" s="21">
         <f t="shared" si="10"/>
         <v>4661.25</v>
       </c>
-      <c r="M8" s="58">
+      <c r="M8" s="21">
         <f t="shared" si="8"/>
         <v>-11722.5</v>
       </c>
-      <c r="N8" s="56" t="str">
+      <c r="N8" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O8" s="70">
+      <c r="O8" s="26">
         <f t="shared" si="12"/>
         <v>1.5</v>
       </c>
-      <c r="P8" s="58">
+      <c r="P8" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="9" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B9" s="41">
+      <c r="B9" s="20">
         <v>3</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="11">
         <f t="shared" si="0"/>
         <v>359.37000000000012</v>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="11">
         <f t="shared" si="1"/>
         <v>359.37000000000012</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F9" s="53">
+      <c r="F9" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G9" s="58">
+      <c r="G9" s="21">
         <f t="shared" si="4"/>
         <v>12478.125000000004</v>
       </c>
-      <c r="H9" s="58">
+      <c r="H9" s="21">
         <f t="shared" si="5"/>
         <v>2640</v>
       </c>
-      <c r="I9" s="58">
+      <c r="I9" s="21">
         <f t="shared" si="6"/>
         <v>15118.125000000004</v>
       </c>
-      <c r="J9" s="58">
+      <c r="J9" s="21">
         <f t="shared" si="7"/>
         <v>35118.125</v>
       </c>
-      <c r="K9" s="58">
+      <c r="K9" s="21">
         <f t="shared" si="9"/>
         <v>5795.625</v>
       </c>
-      <c r="L9" s="58">
+      <c r="L9" s="21">
         <f t="shared" si="10"/>
         <v>5039.3750000000009</v>
       </c>
-      <c r="M9" s="58">
+      <c r="M9" s="21">
         <f t="shared" si="8"/>
         <v>-8718.125</v>
       </c>
-      <c r="N9" s="56" t="str">
+      <c r="N9" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O9" s="70">
+      <c r="O9" s="26">
         <f t="shared" si="12"/>
         <v>2.5</v>
       </c>
-      <c r="P9" s="58">
+      <c r="P9" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B10" s="41">
+      <c r="B10" s="20">
         <v>4</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="11">
         <f t="shared" si="0"/>
         <v>527.07600000000014</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="11">
         <f t="shared" si="1"/>
         <v>527.07600000000014</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10" s="21">
         <f t="shared" si="4"/>
         <v>18301.250000000004</v>
       </c>
-      <c r="H10" s="58">
+      <c r="H10" s="21">
         <f t="shared" si="5"/>
         <v>3520</v>
       </c>
-      <c r="I10" s="58">
+      <c r="I10" s="21">
         <f t="shared" si="6"/>
         <v>21821.250000000004</v>
       </c>
-      <c r="J10" s="58">
+      <c r="J10" s="21">
         <f t="shared" si="7"/>
         <v>41821.25</v>
       </c>
-      <c r="K10" s="58">
+      <c r="K10" s="21">
         <f t="shared" si="9"/>
         <v>6703.125</v>
       </c>
-      <c r="L10" s="58">
+      <c r="L10" s="21">
         <f t="shared" si="10"/>
         <v>5455.3125000000009</v>
       </c>
-      <c r="M10" s="58">
+      <c r="M10" s="21">
         <f t="shared" si="8"/>
         <v>-6621.25</v>
       </c>
-      <c r="N10" s="56" t="str">
+      <c r="N10" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O10" s="70">
+      <c r="O10" s="26">
         <f t="shared" si="12"/>
         <v>3.5</v>
       </c>
-      <c r="P10" s="58">
+      <c r="P10" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B11" s="41">
+      <c r="B11" s="20">
         <v>5</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="11">
         <f t="shared" si="0"/>
         <v>724.72950000000026</v>
       </c>
-      <c r="D11" s="43">
+      <c r="D11" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="11">
         <f t="shared" si="2"/>
         <v>4.7295000000002574</v>
       </c>
-      <c r="F11" s="53">
+      <c r="F11" s="18">
         <f t="shared" si="3"/>
         <v>3.2843750000001786E-3</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="21">
         <f t="shared" si="4"/>
         <v>25082.109375000004</v>
       </c>
-      <c r="H11" s="58">
+      <c r="H11" s="21">
         <f t="shared" si="5"/>
         <v>4400</v>
       </c>
-      <c r="I11" s="58">
+      <c r="I11" s="21">
         <f t="shared" si="6"/>
         <v>29482.109375000004</v>
       </c>
-      <c r="J11" s="58">
+      <c r="J11" s="21">
         <f t="shared" si="7"/>
         <v>49482.109375</v>
       </c>
-      <c r="K11" s="58">
+      <c r="K11" s="21">
         <f t="shared" si="9"/>
         <v>7660.859375</v>
       </c>
-      <c r="L11" s="58">
+      <c r="L11" s="21">
         <f t="shared" si="10"/>
         <v>5896.4218750000009</v>
       </c>
-      <c r="M11" s="58">
+      <c r="M11" s="21">
         <f t="shared" si="8"/>
         <v>-5482.109375</v>
       </c>
-      <c r="N11" s="56" t="str">
+      <c r="N11" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O11" s="70">
+      <c r="O11" s="26">
         <f t="shared" si="12"/>
         <v>4.5</v>
       </c>
-      <c r="P11" s="58">
+      <c r="P11" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B12" s="41">
+      <c r="B12" s="20">
         <v>6</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="11">
         <f t="shared" si="0"/>
         <v>956.64294000000041</v>
       </c>
-      <c r="D12" s="43">
+      <c r="D12" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="11">
         <f t="shared" si="2"/>
         <v>236.64294000000041</v>
       </c>
-      <c r="F12" s="53">
+      <c r="F12" s="18">
         <f t="shared" si="3"/>
         <v>0.16433537500000028</v>
       </c>
-      <c r="G12" s="58">
+      <c r="G12" s="21">
         <f t="shared" si="4"/>
         <v>29108.384375000009</v>
       </c>
-      <c r="H12" s="58">
+      <c r="H12" s="21">
         <f t="shared" si="5"/>
         <v>5280</v>
       </c>
-      <c r="I12" s="58">
+      <c r="I12" s="21">
         <f t="shared" si="6"/>
         <v>34388.384375000009</v>
       </c>
-      <c r="J12" s="58">
+      <c r="J12" s="21">
         <f t="shared" si="7"/>
         <v>54388.384375000009</v>
       </c>
-      <c r="K12" s="58">
+      <c r="K12" s="21">
         <f t="shared" si="9"/>
         <v>4906.2750000000087</v>
       </c>
-      <c r="L12" s="58">
+      <c r="L12" s="21">
         <f t="shared" si="10"/>
         <v>5731.3973958333345</v>
       </c>
-      <c r="M12" s="58">
+      <c r="M12" s="21">
         <f t="shared" si="8"/>
         <v>-1588.3843750000087</v>
       </c>
-      <c r="N12" s="56" t="str">
+      <c r="N12" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O12" s="70">
+      <c r="O12" s="26">
         <f t="shared" si="12"/>
         <v>5.5</v>
       </c>
-      <c r="P12" s="58">
+      <c r="P12" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B13" s="41">
+      <c r="B13" s="20">
         <v>7</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="11">
         <f t="shared" si="0"/>
         <v>1227.6917730000007</v>
       </c>
-      <c r="D13" s="43">
+      <c r="D13" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E13" s="43">
+      <c r="E13" s="11">
         <f t="shared" si="2"/>
         <v>507.69177300000069</v>
       </c>
-      <c r="F13" s="53">
+      <c r="F13" s="18">
         <f t="shared" si="3"/>
         <v>0.35256373125000046</v>
       </c>
-      <c r="G13" s="58">
+      <c r="G13" s="21">
         <f t="shared" si="4"/>
         <v>33814.09328125001</v>
       </c>
-      <c r="H13" s="58">
+      <c r="H13" s="21">
         <f t="shared" si="5"/>
         <v>6160</v>
       </c>
-      <c r="I13" s="58">
+      <c r="I13" s="21">
         <f t="shared" si="6"/>
         <v>39974.09328125001</v>
       </c>
-      <c r="J13" s="58">
+      <c r="J13" s="21">
         <f t="shared" si="7"/>
         <v>59974.09328125001</v>
       </c>
-      <c r="K13" s="58">
+      <c r="K13" s="21">
         <f t="shared" si="9"/>
         <v>5585.7089062500017</v>
       </c>
-      <c r="L13" s="58">
+      <c r="L13" s="21">
         <f t="shared" si="10"/>
         <v>5710.5847544642875</v>
       </c>
-      <c r="M13" s="58">
+      <c r="M13" s="21">
         <f t="shared" si="8"/>
         <v>1625.9067187499895</v>
       </c>
-      <c r="N13" s="56" t="str">
+      <c r="N13" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O13" s="70">
+      <c r="O13" s="26">
         <f t="shared" si="12"/>
         <v>6.5</v>
       </c>
-      <c r="P13" s="58">
+      <c r="P13" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="14" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B14" s="41">
+      <c r="B14" s="20">
         <v>8</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="11">
         <f t="shared" si="0"/>
         <v>1543.3839432000009</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="11">
         <f t="shared" si="2"/>
         <v>823.38394320000089</v>
       </c>
-      <c r="F14" s="53">
+      <c r="F14" s="18">
         <f t="shared" si="3"/>
         <v>0.57179440500000056</v>
       </c>
-      <c r="G14" s="58">
+      <c r="G14" s="21">
         <f t="shared" si="4"/>
         <v>39294.860125000014</v>
       </c>
-      <c r="H14" s="58">
+      <c r="H14" s="21">
         <f t="shared" si="5"/>
         <v>7040</v>
       </c>
-      <c r="I14" s="58">
+      <c r="I14" s="21">
         <f t="shared" si="6"/>
         <v>46334.860125000014</v>
       </c>
-      <c r="J14" s="58">
+      <c r="J14" s="21">
         <f t="shared" si="7"/>
         <v>66334.860125000007</v>
       </c>
-      <c r="K14" s="58">
+      <c r="K14" s="21">
         <f t="shared" si="9"/>
         <v>6360.766843749996</v>
       </c>
-      <c r="L14" s="58">
+      <c r="L14" s="21">
         <f t="shared" si="10"/>
         <v>5791.8575156250017</v>
       </c>
-      <c r="M14" s="58">
+      <c r="M14" s="21">
         <f t="shared" si="8"/>
         <v>4065.1398749999935</v>
       </c>
-      <c r="N14" s="56" t="str">
+      <c r="N14" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O14" s="70">
+      <c r="O14" s="26">
         <f t="shared" si="12"/>
         <v>7.5</v>
       </c>
-      <c r="P14" s="58">
+      <c r="P14" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="15" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B15" s="41">
+      <c r="B15" s="20">
         <v>9</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="11">
         <f t="shared" si="0"/>
         <v>1909.9376297100011</v>
       </c>
-      <c r="D15" s="43">
+      <c r="D15" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E15" s="43">
+      <c r="E15" s="11">
         <f t="shared" si="2"/>
         <v>1189.9376297100011</v>
       </c>
-      <c r="F15" s="53">
+      <c r="F15" s="18">
         <f t="shared" si="3"/>
         <v>0.82634557618750082</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G15" s="21">
         <f t="shared" si="4"/>
         <v>45658.639404687521</v>
       </c>
-      <c r="H15" s="58">
+      <c r="H15" s="21">
         <f t="shared" si="5"/>
         <v>7920</v>
       </c>
-      <c r="I15" s="58">
+      <c r="I15" s="21">
         <f t="shared" si="6"/>
         <v>53578.639404687521</v>
       </c>
-      <c r="J15" s="58">
+      <c r="J15" s="21">
         <f t="shared" si="7"/>
         <v>73578.639404687521</v>
       </c>
-      <c r="K15" s="58">
+      <c r="K15" s="21">
         <f t="shared" si="9"/>
         <v>7243.7792796875146</v>
       </c>
-      <c r="L15" s="58">
+      <c r="L15" s="21">
         <f t="shared" si="10"/>
         <v>5953.182156076391</v>
       </c>
-      <c r="M15" s="58">
+      <c r="M15" s="21">
         <f t="shared" si="8"/>
         <v>5621.3605953124788</v>
       </c>
-      <c r="N15" s="56" t="str">
+      <c r="N15" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O15" s="70">
+      <c r="O15" s="26">
         <f t="shared" si="12"/>
         <v>8.5</v>
       </c>
-      <c r="P15" s="58">
+      <c r="P15" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="16" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B16" s="41">
+      <c r="B16" s="20">
         <v>10</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="11">
         <f t="shared" si="0"/>
         <v>2334.3682140900019</v>
       </c>
-      <c r="D16" s="43">
+      <c r="D16" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E16" s="43">
+      <c r="E16" s="11">
         <f t="shared" si="2"/>
         <v>1614.3682140900019</v>
       </c>
-      <c r="F16" s="53">
+      <c r="F16" s="18">
         <f t="shared" si="3"/>
         <v>1.1210890375625013</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G16" s="21">
         <f t="shared" si="4"/>
         <v>53027.225939062533</v>
       </c>
-      <c r="H16" s="58">
+      <c r="H16" s="21">
         <f t="shared" si="5"/>
         <v>8800</v>
       </c>
-      <c r="I16" s="58">
+      <c r="I16" s="21">
         <f t="shared" si="6"/>
         <v>61827.225939062533</v>
       </c>
-      <c r="J16" s="58">
+      <c r="J16" s="21">
         <f t="shared" si="7"/>
         <v>81827.22593906254</v>
       </c>
-      <c r="K16" s="58">
+      <c r="K16" s="21">
         <f t="shared" si="9"/>
         <v>8248.5865343750193</v>
       </c>
-      <c r="L16" s="58">
+      <c r="L16" s="21">
         <f t="shared" si="10"/>
         <v>6182.7225939062537</v>
       </c>
-      <c r="M16" s="58">
+      <c r="M16" s="21">
         <f t="shared" si="8"/>
         <v>6172.7740609374596</v>
       </c>
-      <c r="N16" s="56" t="str">
+      <c r="N16" s="8" t="str">
         <f t="shared" si="11"/>
         <v>&lt;-- P ~ MC</v>
       </c>
-      <c r="O16" s="70">
+      <c r="O16" s="26">
         <f t="shared" si="12"/>
         <v>9.5</v>
       </c>
-      <c r="P16" s="58">
+      <c r="P16" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="17" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B17" s="41">
+      <c r="B17" s="20">
         <v>11</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="11">
         <f t="shared" si="0"/>
         <v>2824.5855390489023</v>
       </c>
-      <c r="D17" s="43">
+      <c r="D17" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E17" s="43">
+      <c r="E17" s="11">
         <f t="shared" si="2"/>
         <v>2104.5855390489023</v>
       </c>
-      <c r="F17" s="53">
+      <c r="F17" s="18">
         <f t="shared" si="3"/>
         <v>1.4615177354506266</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G17" s="21">
         <f t="shared" si="4"/>
         <v>61537.943386265666</v>
       </c>
-      <c r="H17" s="58">
+      <c r="H17" s="21">
         <f t="shared" si="5"/>
         <v>9680</v>
       </c>
-      <c r="I17" s="58">
+      <c r="I17" s="21">
         <f t="shared" si="6"/>
         <v>71217.943386265659</v>
       </c>
-      <c r="J17" s="58">
+      <c r="J17" s="21">
         <f t="shared" si="7"/>
         <v>91217.943386265659</v>
       </c>
-      <c r="K17" s="58">
+      <c r="K17" s="21">
         <f t="shared" si="9"/>
         <v>9390.7174472031184</v>
       </c>
-      <c r="L17" s="58">
+      <c r="L17" s="21">
         <f t="shared" si="10"/>
         <v>6474.3584896605144</v>
       </c>
-      <c r="M17" s="58">
+      <c r="M17" s="21">
         <f t="shared" si="8"/>
         <v>5582.0566137343412</v>
       </c>
-      <c r="N17" s="56" t="str">
+      <c r="N17" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O17" s="70">
+      <c r="O17" s="26">
         <f t="shared" si="12"/>
         <v>10.5</v>
       </c>
-      <c r="P17" s="58">
+      <c r="P17" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B18" s="41">
+      <c r="B18" s="20">
         <v>12</v>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="11">
         <f t="shared" si="0"/>
         <v>3389.502646858683</v>
       </c>
-      <c r="D18" s="43">
+      <c r="D18" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E18" s="43">
+      <c r="E18" s="11">
         <f t="shared" si="2"/>
         <v>2669.502646858683</v>
       </c>
-      <c r="F18" s="53">
+      <c r="F18" s="18">
         <f t="shared" si="3"/>
         <v>1.8538212825407521</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G18" s="21">
         <f t="shared" si="4"/>
         <v>71345.532063518796</v>
       </c>
-      <c r="H18" s="58">
+      <c r="H18" s="21">
         <f t="shared" si="5"/>
         <v>10560</v>
       </c>
-      <c r="I18" s="58">
+      <c r="I18" s="21">
         <f t="shared" si="6"/>
         <v>81905.532063518796</v>
       </c>
-      <c r="J18" s="58">
+      <c r="J18" s="21">
         <f t="shared" si="7"/>
         <v>101905.5320635188</v>
       </c>
-      <c r="K18" s="58">
+      <c r="K18" s="21">
         <f t="shared" si="9"/>
         <v>10687.588677253138</v>
       </c>
-      <c r="L18" s="58">
+      <c r="L18" s="21">
         <f t="shared" si="10"/>
         <v>6825.461005293233</v>
       </c>
-      <c r="M18" s="58">
+      <c r="M18" s="21">
         <f t="shared" si="8"/>
         <v>3694.4679364812037</v>
       </c>
-      <c r="N18" s="56" t="str">
+      <c r="N18" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O18" s="70">
+      <c r="O18" s="26">
         <f t="shared" si="12"/>
         <v>11.5</v>
       </c>
-      <c r="P18" s="58">
+      <c r="P18" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B19" s="41">
+      <c r="B19" s="20">
         <v>13</v>
       </c>
-      <c r="C19" s="43">
+      <c r="C19" s="11">
         <f t="shared" si="0"/>
         <v>4039.1573208399304</v>
       </c>
-      <c r="D19" s="43">
+      <c r="D19" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E19" s="43">
+      <c r="E19" s="11">
         <f t="shared" si="2"/>
         <v>3319.1573208399304</v>
       </c>
-      <c r="F19" s="53">
+      <c r="F19" s="18">
         <f t="shared" si="3"/>
         <v>2.3049703616943962</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="21">
         <f t="shared" si="4"/>
         <v>82624.259042359903</v>
       </c>
-      <c r="H19" s="58">
+      <c r="H19" s="21">
         <f t="shared" si="5"/>
         <v>11440</v>
       </c>
-      <c r="I19" s="58">
+      <c r="I19" s="21">
         <f t="shared" si="6"/>
         <v>94064.259042359903</v>
       </c>
-      <c r="J19" s="58">
+      <c r="J19" s="21">
         <f t="shared" si="7"/>
         <v>114064.2590423599</v>
       </c>
-      <c r="K19" s="58">
+      <c r="K19" s="21">
         <f t="shared" si="9"/>
         <v>12158.726978841107</v>
       </c>
-      <c r="L19" s="58">
+      <c r="L19" s="21">
         <f t="shared" si="10"/>
         <v>7235.7122340276846</v>
       </c>
-      <c r="M19" s="58">
+      <c r="M19" s="21">
         <f t="shared" si="8"/>
         <v>335.74095764009689</v>
       </c>
-      <c r="N19" s="56" t="str">
+      <c r="N19" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O19" s="70">
+      <c r="O19" s="26">
         <f t="shared" si="12"/>
         <v>12.5</v>
       </c>
-      <c r="P19" s="58">
+      <c r="P19" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B20" s="41">
+      <c r="B20" s="20">
         <v>14</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="11">
         <f t="shared" si="0"/>
         <v>4784.8479031488414</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="11">
         <f t="shared" si="2"/>
         <v>4064.8479031488414</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="18">
         <f t="shared" si="3"/>
         <v>2.822811043853362</v>
       </c>
-      <c r="G20" s="58">
+      <c r="G20" s="21">
         <f t="shared" si="4"/>
         <v>95570.276096334055</v>
       </c>
-      <c r="H20" s="58">
+      <c r="H20" s="21">
         <f t="shared" si="5"/>
         <v>12320</v>
       </c>
-      <c r="I20" s="58">
+      <c r="I20" s="21">
         <f t="shared" si="6"/>
         <v>107890.27609633406</v>
       </c>
-      <c r="J20" s="58">
+      <c r="J20" s="21">
         <f t="shared" si="7"/>
         <v>127890.27609633406</v>
       </c>
-      <c r="K20" s="58">
+      <c r="K20" s="21">
         <f t="shared" si="9"/>
         <v>13826.017053974152</v>
       </c>
-      <c r="L20" s="58">
+      <c r="L20" s="21">
         <f t="shared" si="10"/>
         <v>7706.4482925952898</v>
       </c>
-      <c r="M20" s="58">
+      <c r="M20" s="21">
         <f t="shared" si="8"/>
         <v>-4690.2760963340552</v>
       </c>
-      <c r="N20" s="56" t="str">
+      <c r="N20" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O20" s="70">
+      <c r="O20" s="26">
         <f t="shared" si="12"/>
         <v>13.5</v>
       </c>
-      <c r="P20" s="58">
+      <c r="P20" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="21" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B21" s="41">
+      <c r="B21" s="20">
         <v>15</v>
       </c>
-      <c r="C21" s="43">
+      <c r="C21" s="11">
         <f t="shared" si="0"/>
         <v>5639.2850287111351</v>
       </c>
-      <c r="D21" s="43">
+      <c r="D21" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="11">
         <f t="shared" si="2"/>
         <v>4919.2850287111351</v>
       </c>
-      <c r="F21" s="53">
+      <c r="F21" s="18">
         <f t="shared" si="3"/>
         <v>3.4161701588271773</v>
       </c>
-      <c r="G21" s="58">
+      <c r="G21" s="21">
         <f t="shared" si="4"/>
         <v>110404.25397067942</v>
       </c>
-      <c r="H21" s="58">
+      <c r="H21" s="21">
         <f t="shared" si="5"/>
         <v>13200</v>
       </c>
-      <c r="I21" s="58">
+      <c r="I21" s="21">
         <f t="shared" si="6"/>
         <v>123604.25397067942</v>
       </c>
-      <c r="J21" s="58">
+      <c r="J21" s="21">
         <f t="shared" si="7"/>
         <v>143604.25397067942</v>
       </c>
-      <c r="K21" s="58">
+      <c r="K21" s="21">
         <f t="shared" si="9"/>
         <v>15713.977874345364</v>
       </c>
-      <c r="L21" s="58">
+      <c r="L21" s="21">
         <f t="shared" si="10"/>
         <v>8240.2835980452946</v>
       </c>
-      <c r="M21" s="58">
+      <c r="M21" s="21">
         <f t="shared" si="8"/>
         <v>-11604.25397067942</v>
       </c>
-      <c r="N21" s="56" t="str">
+      <c r="N21" s="8" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="O21" s="70">
+      <c r="O21" s="26">
         <f t="shared" si="12"/>
         <v>14.5</v>
       </c>
-      <c r="P21" s="58">
+      <c r="P21" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="22" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B22" s="41">
+      <c r="B22" s="20">
         <v>16</v>
       </c>
-      <c r="C22" s="43">
+      <c r="C22" s="11">
         <f t="shared" si="0"/>
         <v>6616.761100354398</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="11">
         <f t="shared" si="2"/>
         <v>5896.761100354398</v>
       </c>
-      <c r="F22" s="53">
+      <c r="F22" s="18">
         <f t="shared" si="3"/>
         <v>4.0949729863572211</v>
       </c>
-      <c r="G22" s="58">
+      <c r="G22" s="21">
         <f t="shared" si="4"/>
         <v>127374.32465893052</v>
       </c>
-      <c r="H22" s="58">
+      <c r="H22" s="21">
         <f t="shared" si="5"/>
         <v>14080</v>
       </c>
-      <c r="I22" s="58">
+      <c r="I22" s="21">
         <f t="shared" si="6"/>
         <v>141454.32465893053</v>
       </c>
-      <c r="J22" s="58">
+      <c r="J22" s="21">
         <f t="shared" si="7"/>
         <v>161454.32465893053</v>
       </c>
-      <c r="K22" s="58">
+      <c r="K22" s="21">
         <f t="shared" si="9"/>
         <v>17850.070688251115</v>
       </c>
-      <c r="L22" s="58">
+      <c r="L22" s="21">
         <f t="shared" si="10"/>
         <v>8840.8952911831584</v>
       </c>
-      <c r="M22" s="58">
+      <c r="M22" s="21">
         <f t="shared" si="8"/>
         <v>-20654.324658930534</v>
       </c>
-      <c r="N22" s="56" t="str">
+      <c r="N22" s="8" t="str">
         <f t="shared" si="11"/>
         <v>INFEASIBLE</v>
       </c>
-      <c r="O22" s="70">
+      <c r="O22" s="26">
         <f t="shared" si="12"/>
         <v>15.5</v>
       </c>
-      <c r="P22" s="58">
+      <c r="P22" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="23" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B23" s="41">
+      <c r="B23" s="20">
         <v>17</v>
       </c>
-      <c r="C23" s="43">
+      <c r="C23" s="11">
         <f t="shared" si="0"/>
         <v>7733.3395360392033</v>
       </c>
-      <c r="D23" s="43">
+      <c r="D23" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E23" s="43">
+      <c r="E23" s="11">
         <f t="shared" si="2"/>
         <v>7013.3395360392033</v>
       </c>
-      <c r="F23" s="53">
+      <c r="F23" s="18">
         <f t="shared" si="3"/>
         <v>4.8703746778050023</v>
       </c>
-      <c r="G23" s="58">
+      <c r="G23" s="21">
         <f t="shared" si="4"/>
         <v>146759.36694512505</v>
       </c>
-      <c r="H23" s="58">
+      <c r="H23" s="21">
         <f t="shared" si="5"/>
         <v>14960</v>
       </c>
-      <c r="I23" s="58">
+      <c r="I23" s="21">
         <f t="shared" si="6"/>
         <v>161719.36694512505</v>
       </c>
-      <c r="J23" s="58">
+      <c r="J23" s="21">
         <f t="shared" si="7"/>
         <v>181719.36694512505</v>
       </c>
-      <c r="K23" s="58">
+      <c r="K23" s="21">
         <f t="shared" si="9"/>
         <v>20265.042286194512</v>
       </c>
-      <c r="L23" s="58">
+      <c r="L23" s="21">
         <f t="shared" si="10"/>
         <v>9512.903937948533</v>
       </c>
-      <c r="M23" s="58">
+      <c r="M23" s="21">
         <f t="shared" si="8"/>
         <v>-32119.366945125046</v>
       </c>
-      <c r="N23" s="56" t="str">
+      <c r="N23" s="8" t="str">
         <f t="shared" si="11"/>
         <v>INFEASIBLE</v>
       </c>
-      <c r="O23" s="70">
+      <c r="O23" s="26">
         <f t="shared" si="12"/>
         <v>16.5</v>
       </c>
-      <c r="P23" s="58">
+      <c r="P23" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="24" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B24" s="41">
+      <c r="B24" s="20">
         <v>18</v>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="11">
         <f t="shared" si="0"/>
         <v>9007.0660478574246</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E24" s="43">
+      <c r="E24" s="11">
         <f t="shared" si="2"/>
         <v>8287.0660478574246</v>
       </c>
-      <c r="F24" s="53">
+      <c r="F24" s="18">
         <f t="shared" si="3"/>
         <v>5.7549069776787674</v>
       </c>
-      <c r="G24" s="58">
+      <c r="G24" s="21">
         <f t="shared" si="4"/>
         <v>168872.67444196917</v>
       </c>
-      <c r="H24" s="58">
+      <c r="H24" s="21">
         <f t="shared" si="5"/>
         <v>15840</v>
       </c>
-      <c r="I24" s="58">
+      <c r="I24" s="21">
         <f t="shared" si="6"/>
         <v>184712.67444196917</v>
       </c>
-      <c r="J24" s="58">
+      <c r="J24" s="21">
         <f t="shared" si="7"/>
         <v>204712.67444196917</v>
       </c>
-      <c r="K24" s="58">
+      <c r="K24" s="21">
         <f t="shared" si="9"/>
         <v>22993.307496844121</v>
       </c>
-      <c r="L24" s="58">
+      <c r="L24" s="21">
         <f t="shared" si="10"/>
         <v>10261.815246776065</v>
       </c>
-      <c r="M24" s="58">
+      <c r="M24" s="21">
         <f t="shared" si="8"/>
         <v>-46312.674441969168</v>
       </c>
-      <c r="N24" s="56" t="str">
+      <c r="N24" s="8" t="str">
         <f t="shared" si="11"/>
         <v>INFEASIBLE</v>
       </c>
-      <c r="O24" s="70">
+      <c r="O24" s="26">
         <f t="shared" si="12"/>
         <v>17.5</v>
       </c>
-      <c r="P24" s="58">
+      <c r="P24" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="25" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B25" s="41">
+      <c r="B25" s="20">
         <v>19</v>
       </c>
-      <c r="C25" s="43">
+      <c r="C25" s="11">
         <f t="shared" si="0"/>
         <v>10458.204466678902</v>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="11">
         <f t="shared" si="2"/>
         <v>9738.2044666789025</v>
       </c>
-      <c r="F25" s="53">
+      <c r="F25" s="18">
         <f t="shared" si="3"/>
         <v>6.7626419907492377</v>
       </c>
-      <c r="G25" s="58">
+      <c r="G25" s="21">
         <f t="shared" si="4"/>
         <v>194066.04976873094</v>
       </c>
-      <c r="H25" s="58">
+      <c r="H25" s="21">
         <f t="shared" si="5"/>
         <v>16720</v>
       </c>
-      <c r="I25" s="58">
+      <c r="I25" s="21">
         <f t="shared" si="6"/>
         <v>210786.04976873094</v>
       </c>
-      <c r="J25" s="58">
+      <c r="J25" s="21">
         <f t="shared" si="7"/>
         <v>230786.04976873094</v>
       </c>
-      <c r="K25" s="58">
+      <c r="K25" s="21">
         <f t="shared" si="9"/>
         <v>26073.375326761772</v>
       </c>
-      <c r="L25" s="58">
+      <c r="L25" s="21">
         <f t="shared" si="10"/>
         <v>11094.002619406892</v>
       </c>
-      <c r="M25" s="58">
+      <c r="M25" s="21">
         <f t="shared" si="8"/>
         <v>-63586.04976873094</v>
       </c>
-      <c r="N25" s="56" t="str">
+      <c r="N25" s="8" t="str">
         <f t="shared" si="11"/>
         <v>INFEASIBLE</v>
       </c>
-      <c r="O25" s="70">
+      <c r="O25" s="26">
         <f t="shared" si="12"/>
         <v>18.5</v>
       </c>
-      <c r="P25" s="58">
+      <c r="P25" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="26" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B26" s="41">
+      <c r="B26" s="20">
         <v>20</v>
       </c>
-      <c r="C26" s="43">
+      <c r="C26" s="11">
         <f t="shared" si="0"/>
         <v>12109.499908786096</v>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="11">
         <f t="shared" si="1"/>
         <v>720</v>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="11">
         <f t="shared" si="2"/>
         <v>11389.499908786096</v>
       </c>
-      <c r="F26" s="53">
+      <c r="F26" s="18">
         <f t="shared" si="3"/>
         <v>7.9093749366570112</v>
       </c>
-      <c r="G26" s="58">
+      <c r="G26" s="21">
         <f t="shared" si="4"/>
         <v>222734.37341642528</v>
       </c>
-      <c r="H26" s="58">
+      <c r="H26" s="21">
         <f t="shared" si="5"/>
         <v>17600</v>
       </c>
-      <c r="I26" s="58">
+      <c r="I26" s="21">
         <f t="shared" si="6"/>
         <v>240334.37341642528</v>
       </c>
-      <c r="J26" s="58">
+      <c r="J26" s="21">
         <f t="shared" si="7"/>
         <v>260334.37341642528</v>
       </c>
-      <c r="K26" s="58">
+      <c r="K26" s="21">
         <f t="shared" si="9"/>
         <v>29548.323647694342</v>
       </c>
-      <c r="L26" s="58">
+      <c r="L26" s="21">
         <f t="shared" si="10"/>
         <v>12016.718670821265</v>
       </c>
-      <c r="M26" s="58">
+      <c r="M26" s="21">
         <f t="shared" si="8"/>
         <v>-84334.373416425282</v>
       </c>
-      <c r="N26" s="69" t="str">
+      <c r="N26" s="8" t="str">
         <f>IF(F26&gt;temp_max,"INFEASIBLE","")</f>
         <v>INFEASIBLE</v>
       </c>
-      <c r="O26" s="70">
+      <c r="O26" s="26">
         <f t="shared" si="12"/>
         <v>19.5</v>
       </c>
-      <c r="P26" s="58">
+      <c r="P26" s="21">
         <f t="shared" si="13"/>
         <v>8800</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="40"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
     </row>
     <row r="30" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B30" s="44" t="s">
+      <c r="B30" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C30" s="44" t="s">
+      <c r="C30" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D30" s="44" t="s">
+      <c r="D30" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E30" s="44" t="s">
+      <c r="E30" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F30" s="44" t="s">
+      <c r="F30" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G30" s="44" t="s">
+      <c r="G30" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H30" s="44" t="s">
+      <c r="H30" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="I30" s="44" t="s">
+      <c r="I30" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="J30" s="44" t="s">
+      <c r="J30" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="K30" s="44" t="s">
+      <c r="K30" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="L30" s="44" t="s">
+      <c r="L30" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="M30" s="44" t="s">
+      <c r="M30" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="N30" s="44" t="s">
+      <c r="N30" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="O30" s="44" t="s">
+      <c r="O30" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="P30" s="44" t="s">
+      <c r="P30" s="12" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="31" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B31" s="41">
-        <v>0</v>
-      </c>
-      <c r="C31" s="66">
+      <c r="B31" s="20">
+        <v>0</v>
+      </c>
+      <c r="C31" s="11">
         <f t="shared" ref="C31:C51" si="14">B31*laborwk_carrot*season_wks*(1+dim_carrot)^B31</f>
         <v>0</v>
       </c>
-      <c r="D31" s="66">
+      <c r="D31" s="11">
         <f t="shared" ref="D31:D51" si="15">MIN(perm_field_hrs,C31)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="43">
+      <c r="E31" s="11">
         <f t="shared" ref="E31:E51" si="16">C31-D31</f>
         <v>0</v>
       </c>
-      <c r="F31" s="67">
+      <c r="F31" s="18">
         <f t="shared" ref="F31:F51" si="17">E31/temp_hrs_each</f>
         <v>0</v>
       </c>
-      <c r="G31" s="68">
+      <c r="G31" s="21">
         <f t="shared" ref="G31:G51" si="18">D31*wage_perm+E31*wage_temp</f>
         <v>0</v>
       </c>
-      <c r="H31" s="68">
+      <c r="H31" s="21">
         <f t="shared" ref="H31:H51" si="19">B31*fert_carrot</f>
         <v>0</v>
       </c>
-      <c r="I31" s="58">
+      <c r="I31" s="21">
         <f t="shared" ref="I31:I51" si="20">G31+H31</f>
         <v>0</v>
       </c>
-      <c r="J31" s="68">
+      <c r="J31" s="21">
         <f t="shared" ref="J31:J51" si="21">I31+costs_fixed</f>
         <v>20000</v>
       </c>
-      <c r="M31" s="68">
+      <c r="M31" s="21">
         <f t="shared" ref="M31:M51" si="22">B31*price_carrot-J31</f>
         <v>-20000</v>
       </c>
     </row>
     <row r="32" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B32" s="41">
+      <c r="B32" s="20">
         <v>1</v>
       </c>
-      <c r="C32" s="43">
+      <c r="C32" s="11">
         <f t="shared" si="14"/>
         <v>30.749999999999996</v>
       </c>
-      <c r="D32" s="43">
+      <c r="D32" s="11">
         <f t="shared" si="15"/>
         <v>30.749999999999996</v>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G32" s="58">
+      <c r="G32" s="21">
         <f t="shared" si="18"/>
         <v>1067.7083333333333</v>
       </c>
-      <c r="H32" s="58">
+      <c r="H32" s="21">
         <f t="shared" si="19"/>
         <v>440</v>
       </c>
-      <c r="I32" s="58">
+      <c r="I32" s="21">
         <f t="shared" si="20"/>
         <v>1507.7083333333333</v>
       </c>
-      <c r="J32" s="58">
+      <c r="J32" s="21">
         <f t="shared" si="21"/>
         <v>21507.708333333332</v>
       </c>
-      <c r="K32" s="58">
+      <c r="K32" s="21">
         <f t="shared" ref="K32:K51" si="23">J32-J31</f>
         <v>1507.7083333333321</v>
       </c>
-      <c r="L32" s="58">
+      <c r="L32" s="21">
         <f t="shared" ref="L32:L51" si="24">I32/B32</f>
         <v>1507.7083333333333</v>
       </c>
-      <c r="M32" s="58">
+      <c r="M32" s="21">
         <f t="shared" si="22"/>
         <v>-19413.708333333332</v>
       </c>
-      <c r="N32" s="69" t="str">
+      <c r="N32" s="8" t="str">
         <f t="shared" ref="N32:N50" si="25">IF(F32&gt;temp_max,"INFEASIBLE",IF(AND(price_carrot&gt;K32,price_carrot&lt;K33),"&lt;-- P ~ MC",""))</f>
         <v/>
       </c>
-      <c r="O32" s="70">
+      <c r="O32" s="26">
         <f t="shared" ref="O32:O51" si="26">(B32+B31)/2</f>
         <v>0.5</v>
       </c>
-      <c r="P32" s="68">
+      <c r="P32" s="21">
         <f t="shared" ref="P32:P51" si="27">price_carrot</f>
         <v>2094</v>
       </c>
     </row>
     <row r="33" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B33" s="41">
+      <c r="B33" s="20">
         <v>2</v>
       </c>
-      <c r="C33" s="43">
+      <c r="C33" s="11">
         <f t="shared" si="14"/>
         <v>63.037499999999994</v>
       </c>
-      <c r="D33" s="43">
+      <c r="D33" s="11">
         <f t="shared" si="15"/>
         <v>63.037499999999994</v>
       </c>
-      <c r="E33" s="43">
+      <c r="E33" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F33" s="53">
+      <c r="F33" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G33" s="58">
+      <c r="G33" s="21">
         <f t="shared" si="18"/>
         <v>2188.802083333333</v>
       </c>
-      <c r="H33" s="58">
+      <c r="H33" s="21">
         <f t="shared" si="19"/>
         <v>880</v>
       </c>
-      <c r="I33" s="58">
+      <c r="I33" s="21">
         <f t="shared" si="20"/>
         <v>3068.802083333333</v>
       </c>
-      <c r="J33" s="58">
+      <c r="J33" s="21">
         <f t="shared" si="21"/>
         <v>23068.802083333332</v>
       </c>
-      <c r="K33" s="58">
+      <c r="K33" s="21">
         <f t="shared" si="23"/>
         <v>1561.09375</v>
       </c>
-      <c r="L33" s="58">
+      <c r="L33" s="21">
         <f t="shared" si="24"/>
         <v>1534.4010416666665</v>
       </c>
-      <c r="M33" s="58">
+      <c r="M33" s="21">
         <f t="shared" si="22"/>
         <v>-18880.802083333332</v>
       </c>
-      <c r="N33" s="56" t="str">
+      <c r="N33" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O33" s="70">
+      <c r="O33" s="26">
         <f t="shared" si="26"/>
         <v>1.5</v>
       </c>
-      <c r="P33" s="58">
+      <c r="P33" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B34" s="41">
+      <c r="B34" s="20">
         <v>3</v>
       </c>
-      <c r="C34" s="43">
+      <c r="C34" s="11">
         <f t="shared" si="14"/>
         <v>96.920156249999991</v>
       </c>
-      <c r="D34" s="43">
+      <c r="D34" s="11">
         <f t="shared" si="15"/>
         <v>96.920156249999991</v>
       </c>
-      <c r="E34" s="43">
+      <c r="E34" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F34" s="53">
+      <c r="F34" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G34" s="58">
+      <c r="G34" s="21">
         <f t="shared" si="18"/>
         <v>3365.2832031249995</v>
       </c>
-      <c r="H34" s="58">
+      <c r="H34" s="21">
         <f t="shared" si="19"/>
         <v>1320</v>
       </c>
-      <c r="I34" s="58">
+      <c r="I34" s="21">
         <f t="shared" si="20"/>
         <v>4685.283203125</v>
       </c>
-      <c r="J34" s="58">
+      <c r="J34" s="21">
         <f t="shared" si="21"/>
         <v>24685.283203125</v>
       </c>
-      <c r="K34" s="58">
+      <c r="K34" s="21">
         <f t="shared" si="23"/>
         <v>1616.4811197916679</v>
       </c>
-      <c r="L34" s="58">
+      <c r="L34" s="21">
         <f t="shared" si="24"/>
         <v>1561.7610677083333</v>
       </c>
-      <c r="M34" s="58">
+      <c r="M34" s="21">
         <f t="shared" si="22"/>
         <v>-18403.283203125</v>
       </c>
-      <c r="N34" s="56" t="str">
+      <c r="N34" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O34" s="70">
+      <c r="O34" s="26">
         <f t="shared" si="26"/>
         <v>2.5</v>
       </c>
-      <c r="P34" s="58">
+      <c r="P34" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B35" s="41">
+      <c r="B35" s="20">
         <v>4</v>
       </c>
-      <c r="C35" s="43">
+      <c r="C35" s="11">
         <f t="shared" si="14"/>
         <v>132.45754687499996</v>
       </c>
-      <c r="D35" s="43">
+      <c r="D35" s="11">
         <f t="shared" si="15"/>
         <v>132.45754687499996</v>
       </c>
-      <c r="E35" s="43">
+      <c r="E35" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F35" s="53">
+      <c r="F35" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G35" s="58">
+      <c r="G35" s="21">
         <f t="shared" si="18"/>
         <v>4599.2203776041652</v>
       </c>
-      <c r="H35" s="58">
+      <c r="H35" s="21">
         <f t="shared" si="19"/>
         <v>1760</v>
       </c>
-      <c r="I35" s="58">
+      <c r="I35" s="21">
         <f t="shared" si="20"/>
         <v>6359.2203776041652</v>
       </c>
-      <c r="J35" s="58">
+      <c r="J35" s="21">
         <f t="shared" si="21"/>
         <v>26359.220377604164</v>
       </c>
-      <c r="K35" s="58">
+      <c r="K35" s="21">
         <f t="shared" si="23"/>
         <v>1673.9371744791642</v>
       </c>
-      <c r="L35" s="58">
+      <c r="L35" s="21">
         <f t="shared" si="24"/>
         <v>1589.8050944010413</v>
       </c>
-      <c r="M35" s="58">
+      <c r="M35" s="21">
         <f t="shared" si="22"/>
         <v>-17983.220377604164</v>
       </c>
-      <c r="N35" s="56" t="str">
+      <c r="N35" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O35" s="70">
+      <c r="O35" s="26">
         <f t="shared" si="26"/>
         <v>3.5</v>
       </c>
-      <c r="P35" s="58">
+      <c r="P35" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B36" s="41">
+      <c r="B36" s="20">
         <v>5</v>
       </c>
-      <c r="C36" s="43">
+      <c r="C36" s="11">
         <f t="shared" si="14"/>
         <v>169.71123193359369</v>
       </c>
-      <c r="D36" s="43">
+      <c r="D36" s="11">
         <f t="shared" si="15"/>
         <v>169.71123193359369</v>
       </c>
-      <c r="E36" s="43">
+      <c r="E36" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F36" s="53">
+      <c r="F36" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G36" s="58">
+      <c r="G36" s="21">
         <f t="shared" si="18"/>
         <v>5892.7511088053361</v>
       </c>
-      <c r="H36" s="58">
+      <c r="H36" s="21">
         <f t="shared" si="19"/>
         <v>2200</v>
       </c>
-      <c r="I36" s="58">
+      <c r="I36" s="21">
         <f t="shared" si="20"/>
         <v>8092.7511088053361</v>
       </c>
-      <c r="J36" s="58">
+      <c r="J36" s="21">
         <f t="shared" si="21"/>
         <v>28092.751108805336</v>
       </c>
-      <c r="K36" s="58">
+      <c r="K36" s="21">
         <f t="shared" si="23"/>
         <v>1733.5307312011719</v>
       </c>
-      <c r="L36" s="58">
+      <c r="L36" s="21">
         <f t="shared" si="24"/>
         <v>1618.5502217610672</v>
       </c>
-      <c r="M36" s="58">
+      <c r="M36" s="21">
         <f t="shared" si="22"/>
         <v>-17622.751108805336</v>
       </c>
-      <c r="N36" s="56" t="str">
+      <c r="N36" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O36" s="70">
+      <c r="O36" s="26">
         <f t="shared" si="26"/>
         <v>4.5</v>
       </c>
-      <c r="P36" s="58">
+      <c r="P36" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B37" s="41">
+      <c r="B37" s="20">
         <v>6</v>
       </c>
-      <c r="C37" s="43">
+      <c r="C37" s="11">
         <f t="shared" si="14"/>
         <v>208.74481527832023</v>
       </c>
-      <c r="D37" s="43">
+      <c r="D37" s="11">
         <f t="shared" si="15"/>
         <v>208.74481527832023</v>
       </c>
-      <c r="E37" s="43">
+      <c r="E37" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F37" s="53">
+      <c r="F37" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G37" s="58">
+      <c r="G37" s="21">
         <f t="shared" si="18"/>
         <v>7248.0838638305631</v>
       </c>
-      <c r="H37" s="58">
+      <c r="H37" s="21">
         <f t="shared" si="19"/>
         <v>2640</v>
       </c>
-      <c r="I37" s="58">
+      <c r="I37" s="21">
         <f t="shared" si="20"/>
         <v>9888.0838638305631</v>
       </c>
-      <c r="J37" s="58">
+      <c r="J37" s="21">
         <f t="shared" si="21"/>
         <v>29888.083863830565</v>
       </c>
-      <c r="K37" s="58">
+      <c r="K37" s="21">
         <f t="shared" si="23"/>
         <v>1795.3327550252288</v>
       </c>
-      <c r="L37" s="58">
+      <c r="L37" s="21">
         <f t="shared" si="24"/>
         <v>1648.0139773050939</v>
       </c>
-      <c r="M37" s="58">
+      <c r="M37" s="21">
         <f t="shared" si="22"/>
         <v>-17324.083863830565</v>
       </c>
-      <c r="N37" s="56" t="str">
+      <c r="N37" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O37" s="70">
+      <c r="O37" s="26">
         <f t="shared" si="26"/>
         <v>5.5</v>
       </c>
-      <c r="P37" s="58">
+      <c r="P37" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B38" s="41">
+      <c r="B38" s="20">
         <v>7</v>
       </c>
-      <c r="C38" s="43">
+      <c r="C38" s="11">
         <f t="shared" si="14"/>
         <v>249.62400827032465</v>
       </c>
-      <c r="D38" s="43">
+      <c r="D38" s="11">
         <f t="shared" si="15"/>
         <v>249.62400827032465</v>
       </c>
-      <c r="E38" s="43">
+      <c r="E38" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F38" s="53">
+      <c r="F38" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G38" s="58">
+      <c r="G38" s="21">
         <f t="shared" si="18"/>
         <v>8667.50028716405</v>
       </c>
-      <c r="H38" s="58">
+      <c r="H38" s="21">
         <f t="shared" si="19"/>
         <v>3080</v>
       </c>
-      <c r="I38" s="58">
+      <c r="I38" s="21">
         <f t="shared" si="20"/>
         <v>11747.50028716405</v>
       </c>
-      <c r="J38" s="58">
+      <c r="J38" s="21">
         <f t="shared" si="21"/>
         <v>31747.50028716405</v>
       </c>
-      <c r="K38" s="58">
+      <c r="K38" s="21">
         <f t="shared" si="23"/>
         <v>1859.416423333485</v>
       </c>
-      <c r="L38" s="58">
+      <c r="L38" s="21">
         <f t="shared" si="24"/>
         <v>1678.2143267377214</v>
       </c>
-      <c r="M38" s="58">
+      <c r="M38" s="21">
         <f t="shared" si="22"/>
         <v>-17089.50028716405</v>
       </c>
-      <c r="N38" s="56" t="str">
+      <c r="N38" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O38" s="70">
+      <c r="O38" s="26">
         <f t="shared" si="26"/>
         <v>6.5</v>
       </c>
-      <c r="P38" s="58">
+      <c r="P38" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B39" s="41">
+      <c r="B39" s="20">
         <v>8</v>
       </c>
-      <c r="C39" s="43">
+      <c r="C39" s="11">
         <f t="shared" si="14"/>
         <v>292.41669540238024</v>
       </c>
-      <c r="D39" s="43">
+      <c r="D39" s="11">
         <f t="shared" si="15"/>
         <v>292.41669540238024</v>
       </c>
-      <c r="E39" s="43">
+      <c r="E39" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F39" s="53">
+      <c r="F39" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G39" s="58">
+      <c r="G39" s="21">
         <f t="shared" si="18"/>
         <v>10153.357479249315</v>
       </c>
-      <c r="H39" s="58">
+      <c r="H39" s="21">
         <f t="shared" si="19"/>
         <v>3520</v>
       </c>
-      <c r="I39" s="58">
+      <c r="I39" s="21">
         <f t="shared" si="20"/>
         <v>13673.357479249315</v>
       </c>
-      <c r="J39" s="58">
+      <c r="J39" s="21">
         <f t="shared" si="21"/>
         <v>33673.357479249316</v>
       </c>
-      <c r="K39" s="58">
+      <c r="K39" s="21">
         <f t="shared" si="23"/>
         <v>1925.8571920852664</v>
       </c>
-      <c r="L39" s="58">
+      <c r="L39" s="21">
         <f t="shared" si="24"/>
         <v>1709.1696849061643</v>
       </c>
-      <c r="M39" s="58">
+      <c r="M39" s="21">
         <f t="shared" si="22"/>
         <v>-16921.357479249316</v>
       </c>
-      <c r="N39" s="56" t="str">
+      <c r="N39" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O39" s="70">
+      <c r="O39" s="26">
         <f t="shared" si="26"/>
         <v>7.5</v>
       </c>
-      <c r="P39" s="58">
+      <c r="P39" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B40" s="41">
+      <c r="B40" s="20">
         <v>9</v>
       </c>
-      <c r="C40" s="43">
+      <c r="C40" s="11">
         <f t="shared" si="14"/>
         <v>337.19300188586965</v>
       </c>
-      <c r="D40" s="43">
+      <c r="D40" s="11">
         <f t="shared" si="15"/>
         <v>337.19300188586965</v>
       </c>
-      <c r="E40" s="43">
+      <c r="E40" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F40" s="53">
+      <c r="F40" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G40" s="58">
+      <c r="G40" s="21">
         <f t="shared" si="18"/>
         <v>11708.090343259362</v>
       </c>
-      <c r="H40" s="58">
+      <c r="H40" s="21">
         <f t="shared" si="19"/>
         <v>3960</v>
       </c>
-      <c r="I40" s="58">
+      <c r="I40" s="21">
         <f t="shared" si="20"/>
         <v>15668.090343259362</v>
       </c>
-      <c r="J40" s="58">
+      <c r="J40" s="21">
         <f t="shared" si="21"/>
         <v>35668.090343259362</v>
       </c>
-      <c r="K40" s="58">
+      <c r="K40" s="21">
         <f t="shared" si="23"/>
         <v>1994.7328640100459</v>
       </c>
-      <c r="L40" s="58">
+      <c r="L40" s="21">
         <f t="shared" si="24"/>
         <v>1740.898927028818</v>
       </c>
-      <c r="M40" s="58">
+      <c r="M40" s="21">
         <f t="shared" si="22"/>
         <v>-16822.090343259362</v>
       </c>
-      <c r="N40" s="56" t="str">
+      <c r="N40" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O40" s="70">
+      <c r="O40" s="26">
         <f t="shared" si="26"/>
         <v>8.5</v>
       </c>
-      <c r="P40" s="58">
+      <c r="P40" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B41" s="41">
+      <c r="B41" s="20">
         <v>10</v>
       </c>
-      <c r="C41" s="43">
+      <c r="C41" s="11">
         <f t="shared" si="14"/>
         <v>384.02536325890713</v>
       </c>
-      <c r="D41" s="43">
+      <c r="D41" s="11">
         <f t="shared" si="15"/>
         <v>384.02536325890713</v>
       </c>
-      <c r="E41" s="43">
+      <c r="E41" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F41" s="53">
+      <c r="F41" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G41" s="58">
+      <c r="G41" s="21">
         <f t="shared" si="18"/>
         <v>13334.214002045386</v>
       </c>
-      <c r="H41" s="58">
+      <c r="H41" s="21">
         <f t="shared" si="19"/>
         <v>4400</v>
       </c>
-      <c r="I41" s="58">
+      <c r="I41" s="21">
         <f t="shared" si="20"/>
         <v>17734.214002045388</v>
       </c>
-      <c r="J41" s="58">
+      <c r="J41" s="21">
         <f t="shared" si="21"/>
         <v>37734.214002045388</v>
       </c>
-      <c r="K41" s="58">
+      <c r="K41" s="21">
         <f t="shared" si="23"/>
         <v>2066.1236587860258</v>
       </c>
-      <c r="L41" s="58">
+      <c r="L41" s="21">
         <f t="shared" si="24"/>
         <v>1773.4214002045387</v>
       </c>
-      <c r="M41" s="58">
+      <c r="M41" s="21">
         <f t="shared" si="22"/>
         <v>-16794.214002045388</v>
       </c>
-      <c r="N41" s="56" t="str">
+      <c r="N41" s="8" t="str">
         <f t="shared" si="25"/>
         <v>&lt;-- P ~ MC</v>
       </c>
-      <c r="O41" s="70">
+      <c r="O41" s="26">
         <f t="shared" si="26"/>
         <v>9.5</v>
       </c>
-      <c r="P41" s="58">
+      <c r="P41" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B42" s="41">
+      <c r="B42" s="20">
         <v>11</v>
       </c>
-      <c r="C42" s="43">
+      <c r="C42" s="11">
         <f t="shared" si="14"/>
         <v>432.98859707441784</v>
       </c>
-      <c r="D42" s="43">
+      <c r="D42" s="11">
         <f t="shared" si="15"/>
         <v>432.98859707441784</v>
       </c>
-      <c r="E42" s="43">
+      <c r="E42" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F42" s="53">
+      <c r="F42" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G42" s="58">
+      <c r="G42" s="21">
         <f t="shared" si="18"/>
         <v>15034.326287306174</v>
       </c>
-      <c r="H42" s="58">
+      <c r="H42" s="21">
         <f t="shared" si="19"/>
         <v>4840</v>
       </c>
-      <c r="I42" s="58">
+      <c r="I42" s="21">
         <f t="shared" si="20"/>
         <v>19874.326287306176</v>
       </c>
-      <c r="J42" s="58">
+      <c r="J42" s="21">
         <f t="shared" si="21"/>
         <v>39874.326287306176</v>
       </c>
-      <c r="K42" s="58">
+      <c r="K42" s="21">
         <f t="shared" si="23"/>
         <v>2140.1122852607878</v>
       </c>
-      <c r="L42" s="58">
+      <c r="L42" s="21">
         <f t="shared" si="24"/>
         <v>1806.7569352096523</v>
       </c>
-      <c r="M42" s="58">
+      <c r="M42" s="21">
         <f t="shared" si="22"/>
         <v>-16840.326287306176</v>
       </c>
-      <c r="N42" s="56" t="str">
+      <c r="N42" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O42" s="70">
+      <c r="O42" s="26">
         <f t="shared" si="26"/>
         <v>10.5</v>
       </c>
-      <c r="P42" s="58">
+      <c r="P42" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B43" s="41">
+      <c r="B43" s="20">
         <v>12</v>
       </c>
-      <c r="C43" s="43">
+      <c r="C43" s="11">
         <f t="shared" si="14"/>
         <v>484.15997672866712</v>
       </c>
-      <c r="D43" s="43">
+      <c r="D43" s="11">
         <f t="shared" si="15"/>
         <v>484.15997672866712</v>
       </c>
-      <c r="E43" s="43">
+      <c r="E43" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F43" s="53">
+      <c r="F43" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G43" s="58">
+      <c r="G43" s="21">
         <f t="shared" si="18"/>
         <v>16811.11030307872</v>
       </c>
-      <c r="H43" s="58">
+      <c r="H43" s="21">
         <f t="shared" si="19"/>
         <v>5280</v>
       </c>
-      <c r="I43" s="58">
+      <c r="I43" s="21">
         <f t="shared" si="20"/>
         <v>22091.11030307872</v>
       </c>
-      <c r="J43" s="58">
+      <c r="J43" s="21">
         <f t="shared" si="21"/>
         <v>42091.11030307872</v>
       </c>
-      <c r="K43" s="58">
+      <c r="K43" s="21">
         <f t="shared" si="23"/>
         <v>2216.7840157725441</v>
       </c>
-      <c r="L43" s="58">
+      <c r="L43" s="21">
         <f t="shared" si="24"/>
         <v>1840.9258585898933</v>
       </c>
-      <c r="M43" s="58">
+      <c r="M43" s="21">
         <f t="shared" si="22"/>
         <v>-16963.11030307872</v>
       </c>
-      <c r="N43" s="56" t="str">
+      <c r="N43" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O43" s="70">
+      <c r="O43" s="26">
         <f t="shared" si="26"/>
         <v>11.5</v>
       </c>
-      <c r="P43" s="58">
+      <c r="P43" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="44" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B44" s="41">
+      <c r="B44" s="20">
         <v>13</v>
       </c>
-      <c r="C44" s="43">
+      <c r="C44" s="11">
         <f t="shared" si="14"/>
         <v>537.61930749245744</v>
       </c>
-      <c r="D44" s="43">
+      <c r="D44" s="11">
         <f t="shared" si="15"/>
         <v>537.61930749245744</v>
       </c>
-      <c r="E44" s="43">
+      <c r="E44" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F44" s="53">
+      <c r="F44" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G44" s="58">
+      <c r="G44" s="21">
         <f t="shared" si="18"/>
         <v>18667.337065710326</v>
       </c>
-      <c r="H44" s="58">
+      <c r="H44" s="21">
         <f t="shared" si="19"/>
         <v>5720</v>
       </c>
-      <c r="I44" s="58">
+      <c r="I44" s="21">
         <f t="shared" si="20"/>
         <v>24387.337065710326</v>
       </c>
-      <c r="J44" s="58">
+      <c r="J44" s="21">
         <f t="shared" si="21"/>
         <v>44387.337065710322</v>
       </c>
-      <c r="K44" s="58">
+      <c r="K44" s="21">
         <f t="shared" si="23"/>
         <v>2296.2267626316025</v>
       </c>
-      <c r="L44" s="58">
+      <c r="L44" s="21">
         <f t="shared" si="24"/>
         <v>1875.9490050546406</v>
       </c>
-      <c r="M44" s="58">
+      <c r="M44" s="21">
         <f t="shared" si="22"/>
         <v>-17165.337065710322</v>
       </c>
-      <c r="N44" s="56" t="str">
+      <c r="N44" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O44" s="70">
+      <c r="O44" s="26">
         <f t="shared" si="26"/>
         <v>12.5</v>
       </c>
-      <c r="P44" s="58">
+      <c r="P44" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B45" s="41">
+      <c r="B45" s="20">
         <v>14</v>
       </c>
-      <c r="C45" s="43">
+      <c r="C45" s="11">
         <f t="shared" si="14"/>
         <v>593.44900480898184</v>
       </c>
-      <c r="D45" s="43">
+      <c r="D45" s="11">
         <f t="shared" si="15"/>
         <v>593.44900480898184</v>
       </c>
-      <c r="E45" s="43">
+      <c r="E45" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F45" s="53">
+      <c r="F45" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G45" s="58">
+      <c r="G45" s="21">
         <f t="shared" si="18"/>
         <v>20605.868222534093</v>
       </c>
-      <c r="H45" s="58">
+      <c r="H45" s="21">
         <f t="shared" si="19"/>
         <v>6160</v>
       </c>
-      <c r="I45" s="58">
+      <c r="I45" s="21">
         <f t="shared" si="20"/>
         <v>26765.868222534093</v>
       </c>
-      <c r="J45" s="58">
+      <c r="J45" s="21">
         <f t="shared" si="21"/>
         <v>46765.868222534089</v>
       </c>
-      <c r="K45" s="58">
+      <c r="K45" s="21">
         <f t="shared" si="23"/>
         <v>2378.5311568237667</v>
       </c>
-      <c r="L45" s="58">
+      <c r="L45" s="21">
         <f t="shared" si="24"/>
         <v>1911.8477301810067</v>
       </c>
-      <c r="M45" s="58">
+      <c r="M45" s="21">
         <f t="shared" si="22"/>
         <v>-17449.868222534089</v>
       </c>
-      <c r="N45" s="56" t="str">
+      <c r="N45" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O45" s="70">
+      <c r="O45" s="26">
         <f t="shared" si="26"/>
         <v>13.5</v>
       </c>
-      <c r="P45" s="58">
+      <c r="P45" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="46" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B46" s="41">
+      <c r="B46" s="20">
         <v>15</v>
       </c>
-      <c r="C46" s="43">
+      <c r="C46" s="11">
         <f t="shared" si="14"/>
         <v>651.73417492414967</v>
       </c>
-      <c r="D46" s="43">
+      <c r="D46" s="11">
         <f t="shared" si="15"/>
         <v>651.73417492414967</v>
       </c>
-      <c r="E46" s="43">
+      <c r="E46" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F46" s="53">
+      <c r="F46" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G46" s="58">
+      <c r="G46" s="21">
         <f t="shared" si="18"/>
         <v>22629.658851532975</v>
       </c>
-      <c r="H46" s="58">
+      <c r="H46" s="21">
         <f t="shared" si="19"/>
         <v>6600</v>
       </c>
-      <c r="I46" s="58">
+      <c r="I46" s="21">
         <f t="shared" si="20"/>
         <v>29229.658851532975</v>
       </c>
-      <c r="J46" s="58">
+      <c r="J46" s="21">
         <f t="shared" si="21"/>
         <v>49229.658851532979</v>
       </c>
-      <c r="K46" s="58">
+      <c r="K46" s="21">
         <f t="shared" si="23"/>
         <v>2463.7906289988896</v>
       </c>
-      <c r="L46" s="58">
+      <c r="L46" s="21">
         <f t="shared" si="24"/>
         <v>1948.6439234355316</v>
       </c>
-      <c r="M46" s="58">
+      <c r="M46" s="21">
         <f t="shared" si="22"/>
         <v>-17819.658851532979</v>
       </c>
-      <c r="N46" s="56" t="str">
+      <c r="N46" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O46" s="70">
+      <c r="O46" s="26">
         <f t="shared" si="26"/>
         <v>14.5</v>
       </c>
-      <c r="P46" s="58">
+      <c r="P46" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B47" s="41">
+      <c r="B47" s="20">
         <v>16</v>
       </c>
-      <c r="C47" s="43">
+      <c r="C47" s="11">
         <f t="shared" si="14"/>
         <v>712.5626979170703</v>
       </c>
-      <c r="D47" s="43">
+      <c r="D47" s="11">
         <f t="shared" si="15"/>
         <v>712.5626979170703</v>
       </c>
-      <c r="E47" s="43">
+      <c r="E47" s="11">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="F47" s="53">
+      <c r="F47" s="18">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="G47" s="58">
+      <c r="G47" s="21">
         <f t="shared" si="18"/>
         <v>24741.760344342718</v>
       </c>
-      <c r="H47" s="58">
+      <c r="H47" s="21">
         <f t="shared" si="19"/>
         <v>7040</v>
       </c>
-      <c r="I47" s="58">
+      <c r="I47" s="21">
         <f t="shared" si="20"/>
         <v>31781.760344342718</v>
       </c>
-      <c r="J47" s="58">
+      <c r="J47" s="21">
         <f t="shared" si="21"/>
         <v>51781.760344342722</v>
       </c>
-      <c r="K47" s="58">
+      <c r="K47" s="21">
         <f t="shared" si="23"/>
         <v>2552.1014928097429</v>
       </c>
-      <c r="L47" s="58">
+      <c r="L47" s="21">
         <f t="shared" si="24"/>
         <v>1986.3600215214199</v>
       </c>
-      <c r="M47" s="58">
+      <c r="M47" s="21">
         <f t="shared" si="22"/>
         <v>-18277.760344342722</v>
       </c>
-      <c r="N47" s="56" t="str">
+      <c r="N47" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O47" s="70">
+      <c r="O47" s="26">
         <f t="shared" si="26"/>
         <v>15.5</v>
       </c>
-      <c r="P47" s="58">
+      <c r="P47" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B48" s="41">
+      <c r="B48" s="20">
         <v>17</v>
       </c>
-      <c r="C48" s="43">
+      <c r="C48" s="11">
         <f t="shared" si="14"/>
         <v>776.02531320030937</v>
       </c>
-      <c r="D48" s="43">
+      <c r="D48" s="11">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="E48" s="43">
+      <c r="E48" s="11">
         <f t="shared" si="16"/>
         <v>56.02531320030937</v>
       </c>
-      <c r="F48" s="53">
+      <c r="F48" s="18">
         <f t="shared" si="17"/>
         <v>3.8906467500214842E-2</v>
       </c>
-      <c r="G48" s="58">
+      <c r="G48" s="21">
         <f t="shared" si="18"/>
         <v>25972.66168750537</v>
       </c>
-      <c r="H48" s="58">
+      <c r="H48" s="21">
         <f t="shared" si="19"/>
         <v>7480</v>
       </c>
-      <c r="I48" s="58">
+      <c r="I48" s="21">
         <f t="shared" si="20"/>
         <v>33452.661687505373</v>
       </c>
-      <c r="J48" s="58">
+      <c r="J48" s="21">
         <f t="shared" si="21"/>
         <v>53452.661687505373</v>
       </c>
-      <c r="K48" s="58">
+      <c r="K48" s="21">
         <f t="shared" si="23"/>
         <v>1670.9013431626518</v>
       </c>
-      <c r="L48" s="58">
+      <c r="L48" s="21">
         <f t="shared" si="24"/>
         <v>1967.8036286767867</v>
       </c>
-      <c r="M48" s="58">
+      <c r="M48" s="21">
         <f t="shared" si="22"/>
         <v>-17854.661687505373</v>
       </c>
-      <c r="N48" s="56" t="str">
+      <c r="N48" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O48" s="70">
+      <c r="O48" s="26">
         <f t="shared" si="26"/>
         <v>16.5</v>
       </c>
-      <c r="P48" s="58">
+      <c r="P48" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B49" s="41">
+      <c r="B49" s="20">
         <v>18</v>
       </c>
-      <c r="C49" s="43">
+      <c r="C49" s="11">
         <f t="shared" si="14"/>
         <v>842.2157075615122</v>
       </c>
-      <c r="D49" s="43">
+      <c r="D49" s="11">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="E49" s="43">
+      <c r="E49" s="11">
         <f t="shared" si="16"/>
         <v>122.2157075615122</v>
       </c>
-      <c r="F49" s="53">
+      <c r="F49" s="18">
         <f t="shared" si="17"/>
         <v>8.4872019139939026E-2</v>
       </c>
-      <c r="G49" s="58">
+      <c r="G49" s="21">
         <f t="shared" si="18"/>
         <v>27121.800478498477</v>
       </c>
-      <c r="H49" s="58">
+      <c r="H49" s="21">
         <f t="shared" si="19"/>
         <v>7920</v>
       </c>
-      <c r="I49" s="58">
+      <c r="I49" s="21">
         <f t="shared" si="20"/>
         <v>35041.800478498481</v>
       </c>
-      <c r="J49" s="58">
+      <c r="J49" s="21">
         <f t="shared" si="21"/>
         <v>55041.800478498481</v>
       </c>
-      <c r="K49" s="58">
+      <c r="K49" s="21">
         <f t="shared" si="23"/>
         <v>1589.1387909931072</v>
       </c>
-      <c r="L49" s="58">
+      <c r="L49" s="21">
         <f t="shared" si="24"/>
         <v>1946.7666932499155</v>
       </c>
-      <c r="M49" s="58">
+      <c r="M49" s="21">
         <f t="shared" si="22"/>
         <v>-17349.800478498481</v>
       </c>
-      <c r="N49" s="56" t="str">
+      <c r="N49" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O49" s="70">
+      <c r="O49" s="26">
         <f t="shared" si="26"/>
         <v>17.5</v>
       </c>
-      <c r="P49" s="58">
+      <c r="P49" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B50" s="41">
+      <c r="B50" s="20">
         <v>19</v>
       </c>
-      <c r="C50" s="43">
+      <c r="C50" s="11">
         <f t="shared" si="14"/>
         <v>911.23060582002495</v>
       </c>
-      <c r="D50" s="43">
+      <c r="D50" s="11">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="E50" s="43">
+      <c r="E50" s="11">
         <f t="shared" si="16"/>
         <v>191.23060582002495</v>
       </c>
-      <c r="F50" s="53">
+      <c r="F50" s="18">
         <f t="shared" si="17"/>
         <v>0.13279903181946176</v>
       </c>
-      <c r="G50" s="58">
+      <c r="G50" s="21">
         <f t="shared" si="18"/>
         <v>28319.975795486545</v>
       </c>
-      <c r="H50" s="58">
+      <c r="H50" s="21">
         <f t="shared" si="19"/>
         <v>8360</v>
       </c>
-      <c r="I50" s="58">
+      <c r="I50" s="21">
         <f t="shared" si="20"/>
         <v>36679.975795486549</v>
       </c>
-      <c r="J50" s="58">
+      <c r="J50" s="21">
         <f t="shared" si="21"/>
         <v>56679.975795486549</v>
       </c>
-      <c r="K50" s="58">
+      <c r="K50" s="21">
         <f t="shared" si="23"/>
         <v>1638.1753169880685</v>
       </c>
-      <c r="L50" s="58">
+      <c r="L50" s="21">
         <f t="shared" si="24"/>
         <v>1930.5250418677131</v>
       </c>
-      <c r="M50" s="58">
+      <c r="M50" s="21">
         <f t="shared" si="22"/>
         <v>-16893.975795486549</v>
       </c>
-      <c r="N50" s="56" t="str">
+      <c r="N50" s="8" t="str">
         <f t="shared" si="25"/>
         <v/>
       </c>
-      <c r="O50" s="70">
+      <c r="O50" s="26">
         <f t="shared" si="26"/>
         <v>18.5</v>
       </c>
-      <c r="P50" s="58">
+      <c r="P50" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B51" s="41">
+      <c r="B51" s="20">
         <v>20</v>
       </c>
-      <c r="C51" s="43">
+      <c r="C51" s="11">
         <f t="shared" si="14"/>
         <v>983.16986417423732</v>
       </c>
-      <c r="D51" s="43">
+      <c r="D51" s="11">
         <f t="shared" si="15"/>
         <v>720</v>
       </c>
-      <c r="E51" s="43">
+      <c r="E51" s="11">
         <f t="shared" si="16"/>
         <v>263.16986417423732</v>
       </c>
-      <c r="F51" s="53">
+      <c r="F51" s="18">
         <f t="shared" si="17"/>
         <v>0.18275685012099813</v>
       </c>
-      <c r="G51" s="58">
+      <c r="G51" s="21">
         <f t="shared" si="18"/>
         <v>29568.921253024953</v>
       </c>
-      <c r="H51" s="58">
+      <c r="H51" s="21">
         <f t="shared" si="19"/>
         <v>8800</v>
       </c>
-      <c r="I51" s="58">
+      <c r="I51" s="21">
         <f t="shared" si="20"/>
         <v>38368.92125302495</v>
       </c>
-      <c r="J51" s="58">
+      <c r="J51" s="21">
         <f t="shared" si="21"/>
         <v>58368.92125302495</v>
       </c>
-      <c r="K51" s="58">
+      <c r="K51" s="21">
         <f t="shared" si="23"/>
         <v>1688.9454575384007</v>
       </c>
-      <c r="L51" s="58">
+      <c r="L51" s="21">
         <f t="shared" si="24"/>
         <v>1918.4460626512475</v>
       </c>
-      <c r="M51" s="58">
+      <c r="M51" s="21">
         <f t="shared" si="22"/>
         <v>-16488.92125302495</v>
       </c>
-      <c r="N51" s="69" t="str">
+      <c r="N51" s="8" t="str">
         <f>IF(F51&gt;temp_max,"INFEASIBLE","")</f>
         <v/>
       </c>
-      <c r="O51" s="70">
+      <c r="O51" s="26">
         <f t="shared" si="26"/>
         <v>19.5</v>
       </c>
-      <c r="P51" s="58">
+      <c r="P51" s="21">
         <f t="shared" si="27"/>
         <v>2094</v>
       </c>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B54" s="39" t="s">
+      <c r="B54" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C54" s="40"/>
-      <c r="D54" s="40"/>
-      <c r="E54" s="40"/>
-      <c r="F54" s="40"/>
-      <c r="G54" s="40"/>
-      <c r="H54" s="40"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="40"/>
-      <c r="K54" s="40"/>
-      <c r="L54" s="40"/>
-      <c r="M54" s="40"/>
-      <c r="N54" s="40"/>
-      <c r="O54" s="40"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="7"/>
+      <c r="H54" s="7"/>
+      <c r="I54" s="7"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="7"/>
+      <c r="O54" s="7"/>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B55" s="44" t="s">
+      <c r="B55" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C55" s="44" t="s">
+      <c r="C55" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="D55" s="44" t="s">
+      <c r="D55" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E55" s="44" t="s">
+      <c r="E55" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F55" s="44" t="s">
+      <c r="F55" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="G55" s="44" t="s">
+      <c r="G55" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="H55" s="44" t="s">
+      <c r="H55" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="I55" s="44" t="s">
+      <c r="I55" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="J55" s="44" t="s">
+      <c r="J55" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="K55" s="44" t="s">
+      <c r="K55" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="L55" s="44" t="s">
+      <c r="L55" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="M55" s="44" t="s">
+      <c r="M55" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="N55" s="44" t="s">
+      <c r="N55" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="O55" s="44" t="s">
+      <c r="O55" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="P55" s="44" t="s">
+      <c r="P55" s="12" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B56" s="41">
-        <v>0</v>
-      </c>
-      <c r="C56" s="66">
+      <c r="B56" s="20">
+        <v>0</v>
+      </c>
+      <c r="C56" s="11">
         <f t="shared" ref="C56:C86" si="28">B56*laborwk_mesclun*season_wks*(1+dim_mesclun)^B56</f>
         <v>0</v>
       </c>
-      <c r="D56" s="66">
+      <c r="D56" s="11">
         <f t="shared" ref="D56:D86" si="29">MIN(perm_field_hrs,C56)</f>
         <v>0</v>
       </c>
-      <c r="E56" s="43">
+      <c r="E56" s="11">
         <f t="shared" ref="E56:E86" si="30">C56-D56</f>
         <v>0</v>
       </c>
-      <c r="F56" s="67">
+      <c r="F56" s="18">
         <f t="shared" ref="F56:F86" si="31">E56/temp_hrs_each</f>
         <v>0</v>
       </c>
-      <c r="G56" s="68">
+      <c r="G56" s="21">
         <f t="shared" ref="G56:G86" si="32">D56*wage_perm+E56*wage_temp</f>
         <v>0</v>
       </c>
-      <c r="H56" s="68">
+      <c r="H56" s="21">
         <f t="shared" ref="H56:H86" si="33">B56*fert_mesclun</f>
         <v>0</v>
       </c>
-      <c r="I56" s="58">
+      <c r="I56" s="21">
         <f t="shared" ref="I56:I86" si="34">G56+H56</f>
         <v>0</v>
       </c>
-      <c r="J56" s="68">
+      <c r="J56" s="21">
         <f t="shared" ref="J56:J86" si="35">I56+costs_fixed</f>
         <v>20000</v>
       </c>
-      <c r="M56" s="68">
+      <c r="M56" s="21">
         <f t="shared" ref="M56:M86" si="36">B56*price_mesclun-J56</f>
         <v>-20000</v>
       </c>
     </row>
     <row r="57" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B57" s="41">
+      <c r="B57" s="20">
         <v>1</v>
       </c>
-      <c r="C57" s="43">
+      <c r="C57" s="11">
         <f t="shared" si="28"/>
         <v>45.5625</v>
       </c>
-      <c r="D57" s="43">
+      <c r="D57" s="11">
         <f t="shared" si="29"/>
         <v>45.5625</v>
       </c>
-      <c r="E57" s="43">
+      <c r="E57" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F57" s="53">
+      <c r="F57" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G57" s="58">
+      <c r="G57" s="21">
         <f t="shared" si="32"/>
         <v>1582.03125</v>
       </c>
-      <c r="H57" s="58">
+      <c r="H57" s="21">
         <f t="shared" si="33"/>
         <v>880</v>
       </c>
-      <c r="I57" s="58">
+      <c r="I57" s="21">
         <f t="shared" si="34"/>
         <v>2462.03125</v>
       </c>
-      <c r="J57" s="58">
+      <c r="J57" s="21">
         <f t="shared" si="35"/>
         <v>22462.03125</v>
       </c>
-      <c r="K57" s="58">
+      <c r="K57" s="21">
         <f t="shared" ref="K57:K86" si="37">J57-J56</f>
         <v>2462.03125</v>
       </c>
-      <c r="L57" s="58">
+      <c r="L57" s="21">
         <f t="shared" ref="L57:L86" si="38">I57/B57</f>
         <v>2462.03125</v>
       </c>
-      <c r="M57" s="58">
+      <c r="M57" s="21">
         <f t="shared" si="36"/>
         <v>-19762.03125</v>
       </c>
-      <c r="N57" s="69" t="str">
+      <c r="N57" s="8" t="str">
         <f t="shared" ref="N57:N85" si="39">IF(F57&gt;temp_max,"INFEASIBLE",IF(AND(price_mesclun&gt;K57,price_mesclun&lt;K58),"&lt;-- P ~ MC",""))</f>
         <v/>
       </c>
-      <c r="O57" s="70">
+      <c r="O57" s="26">
         <f t="shared" ref="O57:O86" si="40">(B57+B56)/2</f>
         <v>0.5</v>
       </c>
-      <c r="P57" s="68">
+      <c r="P57" s="21">
         <f t="shared" ref="P57:P86" si="41">price_mesclun</f>
         <v>2700</v>
       </c>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B58" s="41">
+      <c r="B58" s="20">
         <v>2</v>
       </c>
-      <c r="C58" s="43">
+      <c r="C58" s="11">
         <f t="shared" si="28"/>
         <v>92.264062499999994</v>
       </c>
-      <c r="D58" s="43">
+      <c r="D58" s="11">
         <f t="shared" si="29"/>
         <v>92.264062499999994</v>
       </c>
-      <c r="E58" s="43">
+      <c r="E58" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F58" s="53">
+      <c r="F58" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G58" s="58">
+      <c r="G58" s="21">
         <f t="shared" si="32"/>
         <v>3203.6132812499995</v>
       </c>
-      <c r="H58" s="58">
+      <c r="H58" s="21">
         <f t="shared" si="33"/>
         <v>1760</v>
       </c>
-      <c r="I58" s="58">
+      <c r="I58" s="21">
         <f t="shared" si="34"/>
         <v>4963.61328125</v>
       </c>
-      <c r="J58" s="58">
+      <c r="J58" s="21">
         <f t="shared" si="35"/>
         <v>24963.61328125</v>
       </c>
-      <c r="K58" s="58">
+      <c r="K58" s="21">
         <f t="shared" si="37"/>
         <v>2501.58203125</v>
       </c>
-      <c r="L58" s="58">
+      <c r="L58" s="21">
         <f t="shared" si="38"/>
         <v>2481.806640625</v>
       </c>
-      <c r="M58" s="58">
+      <c r="M58" s="21">
         <f t="shared" si="36"/>
         <v>-19563.61328125</v>
       </c>
-      <c r="N58" s="56" t="str">
+      <c r="N58" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O58" s="70">
+      <c r="O58" s="26">
         <f t="shared" si="40"/>
         <v>1.5</v>
       </c>
-      <c r="P58" s="58">
+      <c r="P58" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="59" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B59" s="41">
+      <c r="B59" s="20">
         <v>3</v>
       </c>
-      <c r="C59" s="43">
+      <c r="C59" s="11">
         <f t="shared" si="28"/>
         <v>140.12604492187498</v>
       </c>
-      <c r="D59" s="43">
+      <c r="D59" s="11">
         <f t="shared" si="29"/>
         <v>140.12604492187498</v>
       </c>
-      <c r="E59" s="43">
+      <c r="E59" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F59" s="53">
+      <c r="F59" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G59" s="58">
+      <c r="G59" s="21">
         <f t="shared" si="32"/>
         <v>4865.4876708984366</v>
       </c>
-      <c r="H59" s="58">
+      <c r="H59" s="21">
         <f t="shared" si="33"/>
         <v>2640</v>
       </c>
-      <c r="I59" s="58">
+      <c r="I59" s="21">
         <f t="shared" si="34"/>
         <v>7505.4876708984366</v>
       </c>
-      <c r="J59" s="58">
+      <c r="J59" s="21">
         <f t="shared" si="35"/>
         <v>27505.487670898438</v>
       </c>
-      <c r="K59" s="58">
+      <c r="K59" s="21">
         <f t="shared" si="37"/>
         <v>2541.8743896484375</v>
       </c>
-      <c r="L59" s="58">
+      <c r="L59" s="21">
         <f t="shared" si="38"/>
         <v>2501.829223632812</v>
       </c>
-      <c r="M59" s="58">
+      <c r="M59" s="21">
         <f t="shared" si="36"/>
         <v>-19405.487670898438</v>
       </c>
-      <c r="N59" s="56" t="str">
+      <c r="N59" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O59" s="70">
+      <c r="O59" s="26">
         <f t="shared" si="40"/>
         <v>2.5</v>
       </c>
-      <c r="P59" s="58">
+      <c r="P59" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B60" s="41">
+      <c r="B60" s="20">
         <v>4</v>
       </c>
-      <c r="C60" s="43">
+      <c r="C60" s="11">
         <f t="shared" si="28"/>
         <v>189.17016064453125</v>
       </c>
-      <c r="D60" s="43">
+      <c r="D60" s="11">
         <f t="shared" si="29"/>
         <v>189.17016064453125</v>
       </c>
-      <c r="E60" s="43">
+      <c r="E60" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F60" s="53">
+      <c r="F60" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G60" s="58">
+      <c r="G60" s="21">
         <f t="shared" si="32"/>
         <v>6568.4083557128906</v>
       </c>
-      <c r="H60" s="58">
+      <c r="H60" s="21">
         <f t="shared" si="33"/>
         <v>3520</v>
       </c>
-      <c r="I60" s="58">
+      <c r="I60" s="21">
         <f t="shared" si="34"/>
         <v>10088.408355712891</v>
       </c>
-      <c r="J60" s="58">
+      <c r="J60" s="21">
         <f t="shared" si="35"/>
         <v>30088.408355712891</v>
       </c>
-      <c r="K60" s="58">
+      <c r="K60" s="21">
         <f t="shared" si="37"/>
         <v>2582.9206848144531</v>
       </c>
-      <c r="L60" s="58">
+      <c r="L60" s="21">
         <f t="shared" si="38"/>
         <v>2522.1020889282227</v>
       </c>
-      <c r="M60" s="58">
+      <c r="M60" s="21">
         <f t="shared" si="36"/>
         <v>-19288.408355712891</v>
       </c>
-      <c r="N60" s="56" t="str">
+      <c r="N60" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O60" s="70">
+      <c r="O60" s="26">
         <f t="shared" si="40"/>
         <v>3.5</v>
       </c>
-      <c r="P60" s="58">
+      <c r="P60" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B61" s="41">
+      <c r="B61" s="20">
         <v>5</v>
       </c>
-      <c r="C61" s="43">
+      <c r="C61" s="11">
         <f t="shared" si="28"/>
         <v>239.41848456573481</v>
       </c>
-      <c r="D61" s="43">
+      <c r="D61" s="11">
         <f t="shared" si="29"/>
         <v>239.41848456573481</v>
       </c>
-      <c r="E61" s="43">
+      <c r="E61" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F61" s="53">
+      <c r="F61" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G61" s="58">
+      <c r="G61" s="21">
         <f t="shared" si="32"/>
         <v>8313.1418251991254</v>
       </c>
-      <c r="H61" s="58">
+      <c r="H61" s="21">
         <f t="shared" si="33"/>
         <v>4400</v>
       </c>
-      <c r="I61" s="58">
+      <c r="I61" s="21">
         <f t="shared" si="34"/>
         <v>12713.141825199125</v>
       </c>
-      <c r="J61" s="58">
+      <c r="J61" s="21">
         <f t="shared" si="35"/>
         <v>32713.141825199127</v>
       </c>
-      <c r="K61" s="58">
+      <c r="K61" s="21">
         <f t="shared" si="37"/>
         <v>2624.7334694862366</v>
       </c>
-      <c r="L61" s="58">
+      <c r="L61" s="21">
         <f t="shared" si="38"/>
         <v>2542.628365039825</v>
       </c>
-      <c r="M61" s="58">
+      <c r="M61" s="21">
         <f t="shared" si="36"/>
         <v>-19213.141825199127</v>
       </c>
-      <c r="N61" s="56" t="str">
+      <c r="N61" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O61" s="70">
+      <c r="O61" s="26">
         <f t="shared" si="40"/>
         <v>4.5</v>
       </c>
-      <c r="P61" s="58">
+      <c r="P61" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B62" s="41">
+      <c r="B62" s="20">
         <v>6</v>
       </c>
-      <c r="C62" s="43">
+      <c r="C62" s="11">
         <f t="shared" si="28"/>
         <v>290.89345874736784</v>
       </c>
-      <c r="D62" s="43">
+      <c r="D62" s="11">
         <f t="shared" si="29"/>
         <v>290.89345874736784</v>
       </c>
-      <c r="E62" s="43">
+      <c r="E62" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F62" s="53">
+      <c r="F62" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G62" s="58">
+      <c r="G62" s="21">
         <f t="shared" si="32"/>
         <v>10100.467317616938</v>
       </c>
-      <c r="H62" s="58">
+      <c r="H62" s="21">
         <f t="shared" si="33"/>
         <v>5280</v>
       </c>
-      <c r="I62" s="58">
+      <c r="I62" s="21">
         <f t="shared" si="34"/>
         <v>15380.467317616938</v>
       </c>
-      <c r="J62" s="58">
+      <c r="J62" s="21">
         <f t="shared" si="35"/>
         <v>35380.467317616938</v>
       </c>
-      <c r="K62" s="58">
+      <c r="K62" s="21">
         <f t="shared" si="37"/>
         <v>2667.3254924178109</v>
       </c>
-      <c r="L62" s="58">
+      <c r="L62" s="21">
         <f t="shared" si="38"/>
         <v>2563.4112196028232</v>
       </c>
-      <c r="M62" s="58">
+      <c r="M62" s="21">
         <f t="shared" si="36"/>
         <v>-19180.467317616938</v>
       </c>
-      <c r="N62" s="56" t="str">
+      <c r="N62" s="8" t="str">
         <f t="shared" si="39"/>
         <v>&lt;-- P ~ MC</v>
       </c>
-      <c r="O62" s="70">
+      <c r="O62" s="26">
         <f t="shared" si="40"/>
         <v>5.5</v>
       </c>
-      <c r="P62" s="58">
+      <c r="P62" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B63" s="41">
+      <c r="B63" s="20">
         <v>7</v>
       </c>
-      <c r="C63" s="43">
+      <c r="C63" s="11">
         <f t="shared" si="28"/>
         <v>343.61789814532818</v>
       </c>
-      <c r="D63" s="43">
+      <c r="D63" s="11">
         <f t="shared" si="29"/>
         <v>343.61789814532818</v>
       </c>
-      <c r="E63" s="43">
+      <c r="E63" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F63" s="53">
+      <c r="F63" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="58">
+      <c r="G63" s="21">
         <f t="shared" si="32"/>
         <v>11931.177018935006</v>
       </c>
-      <c r="H63" s="58">
+      <c r="H63" s="21">
         <f t="shared" si="33"/>
         <v>6160</v>
       </c>
-      <c r="I63" s="58">
+      <c r="I63" s="21">
         <f t="shared" si="34"/>
         <v>18091.177018935006</v>
       </c>
-      <c r="J63" s="58">
+      <c r="J63" s="21">
         <f t="shared" si="35"/>
         <v>38091.177018935006</v>
       </c>
-      <c r="K63" s="58">
+      <c r="K63" s="21">
         <f t="shared" si="37"/>
         <v>2710.7097013180683</v>
       </c>
-      <c r="L63" s="58">
+      <c r="L63" s="21">
         <f t="shared" si="38"/>
         <v>2584.453859847858</v>
       </c>
-      <c r="M63" s="58">
+      <c r="M63" s="21">
         <f t="shared" si="36"/>
         <v>-19191.177018935006</v>
       </c>
-      <c r="N63" s="56" t="str">
+      <c r="N63" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O63" s="70">
+      <c r="O63" s="26">
         <f t="shared" si="40"/>
         <v>6.5</v>
       </c>
-      <c r="P63" s="58">
+      <c r="P63" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B64" s="41">
+      <c r="B64" s="20">
         <v>8</v>
       </c>
-      <c r="C64" s="43">
+      <c r="C64" s="11">
         <f t="shared" si="28"/>
         <v>397.61499642530839</v>
       </c>
-      <c r="D64" s="43">
+      <c r="D64" s="11">
         <f t="shared" si="29"/>
         <v>397.61499642530839</v>
       </c>
-      <c r="E64" s="43">
+      <c r="E64" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F64" s="53">
+      <c r="F64" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G64" s="58">
+      <c r="G64" s="21">
         <f t="shared" si="32"/>
         <v>13806.076264767653</v>
       </c>
-      <c r="H64" s="58">
+      <c r="H64" s="21">
         <f t="shared" si="33"/>
         <v>7040</v>
       </c>
-      <c r="I64" s="58">
+      <c r="I64" s="21">
         <f t="shared" si="34"/>
         <v>20846.076264767653</v>
       </c>
-      <c r="J64" s="58">
+      <c r="J64" s="21">
         <f t="shared" si="35"/>
         <v>40846.076264767653</v>
       </c>
-      <c r="K64" s="58">
+      <c r="K64" s="21">
         <f t="shared" si="37"/>
         <v>2754.8992458326466</v>
       </c>
-      <c r="L64" s="58">
+      <c r="L64" s="21">
         <f t="shared" si="38"/>
         <v>2605.7595330959566</v>
       </c>
-      <c r="M64" s="58">
+      <c r="M64" s="21">
         <f t="shared" si="36"/>
         <v>-19246.076264767653</v>
       </c>
-      <c r="N64" s="56" t="str">
+      <c r="N64" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O64" s="70">
+      <c r="O64" s="26">
         <f t="shared" si="40"/>
         <v>7.5</v>
       </c>
-      <c r="P64" s="58">
+      <c r="P64" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="65" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B65" s="41">
+      <c r="B65" s="20">
         <v>9</v>
       </c>
-      <c r="C65" s="43">
+      <c r="C65" s="11">
         <f t="shared" si="28"/>
         <v>452.90833186570285</v>
       </c>
-      <c r="D65" s="43">
+      <c r="D65" s="11">
         <f t="shared" si="29"/>
         <v>452.90833186570285</v>
       </c>
-      <c r="E65" s="43">
+      <c r="E65" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F65" s="53">
+      <c r="F65" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G65" s="58">
+      <c r="G65" s="21">
         <f t="shared" si="32"/>
         <v>15725.983745336904</v>
       </c>
-      <c r="H65" s="58">
+      <c r="H65" s="21">
         <f t="shared" si="33"/>
         <v>7920</v>
       </c>
-      <c r="I65" s="58">
+      <c r="I65" s="21">
         <f t="shared" si="34"/>
         <v>23645.983745336904</v>
       </c>
-      <c r="J65" s="58">
+      <c r="J65" s="21">
         <f t="shared" si="35"/>
         <v>43645.983745336904</v>
       </c>
-      <c r="K65" s="58">
+      <c r="K65" s="21">
         <f t="shared" si="37"/>
         <v>2799.9074805692508</v>
       </c>
-      <c r="L65" s="58">
+      <c r="L65" s="21">
         <f t="shared" si="38"/>
         <v>2627.331527259656</v>
       </c>
-      <c r="M65" s="58">
+      <c r="M65" s="21">
         <f t="shared" si="36"/>
         <v>-19345.983745336904</v>
       </c>
-      <c r="N65" s="56" t="str">
+      <c r="N65" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O65" s="70">
+      <c r="O65" s="26">
         <f t="shared" si="40"/>
         <v>8.5</v>
       </c>
-      <c r="P65" s="58">
+      <c r="P65" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="66" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B66" s="41">
+      <c r="B66" s="20">
         <v>10</v>
       </c>
-      <c r="C66" s="43">
+      <c r="C66" s="11">
         <f t="shared" si="28"/>
         <v>509.52187334891573</v>
       </c>
-      <c r="D66" s="43">
+      <c r="D66" s="11">
         <f t="shared" si="29"/>
         <v>509.52187334891573</v>
       </c>
-      <c r="E66" s="43">
+      <c r="E66" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F66" s="53">
+      <c r="F66" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G66" s="58">
+      <c r="G66" s="21">
         <f t="shared" si="32"/>
         <v>17691.731713504018</v>
       </c>
-      <c r="H66" s="58">
+      <c r="H66" s="21">
         <f t="shared" si="33"/>
         <v>8800</v>
       </c>
-      <c r="I66" s="58">
+      <c r="I66" s="21">
         <f t="shared" si="34"/>
         <v>26491.731713504018</v>
       </c>
-      <c r="J66" s="58">
+      <c r="J66" s="21">
         <f t="shared" si="35"/>
         <v>46491.731713504021</v>
       </c>
-      <c r="K66" s="58">
+      <c r="K66" s="21">
         <f t="shared" si="37"/>
         <v>2845.7479681671175</v>
       </c>
-      <c r="L66" s="58">
+      <c r="L66" s="21">
         <f t="shared" si="38"/>
         <v>2649.1731713504018</v>
       </c>
-      <c r="M66" s="58">
+      <c r="M66" s="21">
         <f t="shared" si="36"/>
         <v>-19491.731713504021</v>
       </c>
-      <c r="N66" s="56" t="str">
+      <c r="N66" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O66" s="70">
+      <c r="O66" s="26">
         <f t="shared" si="40"/>
         <v>9.5</v>
       </c>
-      <c r="P66" s="58">
+      <c r="P66" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="67" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B67" s="41">
+      <c r="B67" s="20">
         <v>11</v>
       </c>
-      <c r="C67" s="43">
+      <c r="C67" s="11">
         <f t="shared" si="28"/>
         <v>567.47998644235474</v>
       </c>
-      <c r="D67" s="43">
+      <c r="D67" s="11">
         <f t="shared" si="29"/>
         <v>567.47998644235474</v>
       </c>
-      <c r="E67" s="43">
+      <c r="E67" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F67" s="53">
+      <c r="F67" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G67" s="58">
+      <c r="G67" s="21">
         <f t="shared" si="32"/>
         <v>19704.166195915095</v>
       </c>
-      <c r="H67" s="58">
+      <c r="H67" s="21">
         <f t="shared" si="33"/>
         <v>9680</v>
       </c>
-      <c r="I67" s="58">
+      <c r="I67" s="21">
         <f t="shared" si="34"/>
         <v>29384.166195915095</v>
       </c>
-      <c r="J67" s="58">
+      <c r="J67" s="21">
         <f t="shared" si="35"/>
         <v>49384.166195915095</v>
       </c>
-      <c r="K67" s="58">
+      <c r="K67" s="21">
         <f t="shared" si="37"/>
         <v>2892.434482411074</v>
       </c>
-      <c r="L67" s="58">
+      <c r="L67" s="21">
         <f t="shared" si="38"/>
         <v>2671.2878359922815</v>
       </c>
-      <c r="M67" s="58">
+      <c r="M67" s="21">
         <f t="shared" si="36"/>
         <v>-19684.166195915095</v>
       </c>
-      <c r="N67" s="56" t="str">
+      <c r="N67" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O67" s="70">
+      <c r="O67" s="26">
         <f t="shared" si="40"/>
         <v>10.5</v>
       </c>
-      <c r="P67" s="58">
+      <c r="P67" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="68" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B68" s="41">
+      <c r="B68" s="20">
         <v>12</v>
       </c>
-      <c r="C68" s="43">
+      <c r="C68" s="11">
         <f t="shared" si="28"/>
         <v>626.80743957041921</v>
       </c>
-      <c r="D68" s="43">
+      <c r="D68" s="11">
         <f t="shared" si="29"/>
         <v>626.80743957041921</v>
       </c>
-      <c r="E68" s="43">
+      <c r="E68" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F68" s="53">
+      <c r="F68" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G68" s="58">
+      <c r="G68" s="21">
         <f t="shared" si="32"/>
         <v>21764.147207306221</v>
       </c>
-      <c r="H68" s="58">
+      <c r="H68" s="21">
         <f t="shared" si="33"/>
         <v>10560</v>
       </c>
-      <c r="I68" s="58">
+      <c r="I68" s="21">
         <f t="shared" si="34"/>
         <v>32324.147207306221</v>
       </c>
-      <c r="J68" s="58">
+      <c r="J68" s="21">
         <f t="shared" si="35"/>
         <v>52324.147207306218</v>
       </c>
-      <c r="K68" s="58">
+      <c r="K68" s="21">
         <f t="shared" si="37"/>
         <v>2939.9810113911226</v>
       </c>
-      <c r="L68" s="58">
+      <c r="L68" s="21">
         <f t="shared" si="38"/>
         <v>2693.6789339421853</v>
       </c>
-      <c r="M68" s="58">
+      <c r="M68" s="21">
         <f t="shared" si="36"/>
         <v>-19924.147207306218</v>
       </c>
-      <c r="N68" s="56" t="str">
+      <c r="N68" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O68" s="70">
+      <c r="O68" s="26">
         <f t="shared" si="40"/>
         <v>11.5</v>
       </c>
-      <c r="P68" s="58">
+      <c r="P68" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="69" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B69" s="41">
+      <c r="B69" s="20">
         <v>13</v>
       </c>
-      <c r="C69" s="43">
+      <c r="C69" s="11">
         <f t="shared" si="28"/>
         <v>687.52941027880343</v>
       </c>
-      <c r="D69" s="43">
+      <c r="D69" s="11">
         <f t="shared" si="29"/>
         <v>687.52941027880343</v>
       </c>
-      <c r="E69" s="43">
+      <c r="E69" s="11">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="F69" s="53">
+      <c r="F69" s="18">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G69" s="58">
+      <c r="G69" s="21">
         <f t="shared" si="32"/>
         <v>23872.548968014009</v>
       </c>
-      <c r="H69" s="58">
+      <c r="H69" s="21">
         <f t="shared" si="33"/>
         <v>11440</v>
       </c>
-      <c r="I69" s="58">
+      <c r="I69" s="21">
         <f t="shared" si="34"/>
         <v>35312.548968014009</v>
       </c>
-      <c r="J69" s="58">
+      <c r="J69" s="21">
         <f t="shared" si="35"/>
         <v>55312.548968014009</v>
       </c>
-      <c r="K69" s="58">
+      <c r="K69" s="21">
         <f t="shared" si="37"/>
         <v>2988.4017607077913</v>
       </c>
-      <c r="L69" s="58">
+      <c r="L69" s="21">
         <f t="shared" si="38"/>
         <v>2716.3499206164624</v>
       </c>
-      <c r="M69" s="58">
+      <c r="M69" s="21">
         <f t="shared" si="36"/>
         <v>-20212.548968014009</v>
       </c>
-      <c r="N69" s="56" t="str">
+      <c r="N69" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O69" s="70">
+      <c r="O69" s="26">
         <f t="shared" si="40"/>
         <v>12.5</v>
       </c>
-      <c r="P69" s="58">
+      <c r="P69" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="70" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B70" s="41">
+      <c r="B70" s="20">
         <v>14</v>
       </c>
-      <c r="C70" s="43">
+      <c r="C70" s="11">
         <f t="shared" si="28"/>
         <v>749.67149159246469</v>
       </c>
-      <c r="D70" s="43">
+      <c r="D70" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E70" s="43">
+      <c r="E70" s="11">
         <f t="shared" si="30"/>
         <v>29.67149159246469</v>
       </c>
-      <c r="F70" s="53">
+      <c r="F70" s="18">
         <f t="shared" si="31"/>
         <v>2.0605202494767147E-2</v>
       </c>
-      <c r="G70" s="58">
+      <c r="G70" s="21">
         <f t="shared" si="32"/>
         <v>25515.130062369179</v>
       </c>
-      <c r="H70" s="58">
+      <c r="H70" s="21">
         <f t="shared" si="33"/>
         <v>12320</v>
       </c>
-      <c r="I70" s="58">
+      <c r="I70" s="21">
         <f t="shared" si="34"/>
         <v>37835.130062369179</v>
       </c>
-      <c r="J70" s="58">
+      <c r="J70" s="21">
         <f t="shared" si="35"/>
         <v>57835.130062369179</v>
       </c>
-      <c r="K70" s="58">
+      <c r="K70" s="21">
         <f t="shared" si="37"/>
         <v>2522.5810943551696</v>
       </c>
-      <c r="L70" s="58">
+      <c r="L70" s="21">
         <f t="shared" si="38"/>
         <v>2702.5092901692269</v>
       </c>
-      <c r="M70" s="58">
+      <c r="M70" s="21">
         <f t="shared" si="36"/>
         <v>-20035.130062369179</v>
       </c>
-      <c r="N70" s="56" t="str">
+      <c r="N70" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O70" s="70">
+      <c r="O70" s="26">
         <f t="shared" si="40"/>
         <v>13.5</v>
       </c>
-      <c r="P70" s="58">
+      <c r="P70" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="71" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B71" s="41">
+      <c r="B71" s="20">
         <v>15</v>
       </c>
-      <c r="C71" s="43">
+      <c r="C71" s="11">
         <f t="shared" si="28"/>
         <v>813.25969846861108</v>
       </c>
-      <c r="D71" s="43">
+      <c r="D71" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E71" s="43">
+      <c r="E71" s="11">
         <f t="shared" si="30"/>
         <v>93.259698468611077</v>
       </c>
-      <c r="F71" s="53">
+      <c r="F71" s="18">
         <f t="shared" si="31"/>
         <v>6.4763679492091025E-2</v>
       </c>
-      <c r="G71" s="58">
+      <c r="G71" s="21">
         <f t="shared" si="32"/>
         <v>26619.091987302276</v>
       </c>
-      <c r="H71" s="58">
+      <c r="H71" s="21">
         <f t="shared" si="33"/>
         <v>13200</v>
       </c>
-      <c r="I71" s="58">
+      <c r="I71" s="21">
         <f t="shared" si="34"/>
         <v>39819.091987302279</v>
       </c>
-      <c r="J71" s="58">
+      <c r="J71" s="21">
         <f t="shared" si="35"/>
         <v>59819.091987302279</v>
       </c>
-      <c r="K71" s="58">
+      <c r="K71" s="21">
         <f t="shared" si="37"/>
         <v>1983.9619249331008</v>
       </c>
-      <c r="L71" s="58">
+      <c r="L71" s="21">
         <f t="shared" si="38"/>
         <v>2654.6061324868188</v>
       </c>
-      <c r="M71" s="58">
+      <c r="M71" s="21">
         <f t="shared" si="36"/>
         <v>-19319.091987302279</v>
       </c>
-      <c r="N71" s="56" t="str">
+      <c r="N71" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O71" s="70">
+      <c r="O71" s="26">
         <f t="shared" si="40"/>
         <v>14.5</v>
       </c>
-      <c r="P71" s="58">
+      <c r="P71" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="72" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B72" s="41">
+      <c r="B72" s="20">
         <v>16</v>
       </c>
-      <c r="C72" s="43">
+      <c r="C72" s="11">
         <f t="shared" si="28"/>
         <v>878.32047434610013</v>
       </c>
-      <c r="D72" s="43">
+      <c r="D72" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E72" s="43">
+      <c r="E72" s="11">
         <f t="shared" si="30"/>
         <v>158.32047434610013</v>
       </c>
-      <c r="F72" s="53">
+      <c r="F72" s="18">
         <f t="shared" si="31"/>
         <v>0.10994477385145843</v>
       </c>
-      <c r="G72" s="58">
+      <c r="G72" s="21">
         <f t="shared" si="32"/>
         <v>27748.619346286461</v>
       </c>
-      <c r="H72" s="58">
+      <c r="H72" s="21">
         <f t="shared" si="33"/>
         <v>14080</v>
       </c>
-      <c r="I72" s="58">
+      <c r="I72" s="21">
         <f t="shared" si="34"/>
         <v>41828.619346286461</v>
       </c>
-      <c r="J72" s="58">
+      <c r="J72" s="21">
         <f t="shared" si="35"/>
         <v>61828.619346286461</v>
       </c>
-      <c r="K72" s="58">
+      <c r="K72" s="21">
         <f t="shared" si="37"/>
         <v>2009.5273589841818</v>
       </c>
-      <c r="L72" s="58">
+      <c r="L72" s="21">
         <f t="shared" si="38"/>
         <v>2614.2887091429038</v>
       </c>
-      <c r="M72" s="58">
+      <c r="M72" s="21">
         <f t="shared" si="36"/>
         <v>-18628.619346286461</v>
       </c>
-      <c r="N72" s="56" t="str">
+      <c r="N72" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O72" s="70">
+      <c r="O72" s="26">
         <f t="shared" si="40"/>
         <v>15.5</v>
       </c>
-      <c r="P72" s="58">
+      <c r="P72" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="73" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B73" s="41">
+      <c r="B73" s="20">
         <v>17</v>
       </c>
-      <c r="C73" s="43">
+      <c r="C73" s="11">
         <f t="shared" si="28"/>
         <v>944.88069779264049</v>
       </c>
-      <c r="D73" s="43">
+      <c r="D73" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E73" s="43">
+      <c r="E73" s="11">
         <f t="shared" si="30"/>
         <v>224.88069779264049</v>
       </c>
-      <c r="F73" s="53">
+      <c r="F73" s="18">
         <f t="shared" si="31"/>
         <v>0.15616715124488922</v>
       </c>
-      <c r="G73" s="58">
+      <c r="G73" s="21">
         <f t="shared" si="32"/>
         <v>28904.178781122231</v>
       </c>
-      <c r="H73" s="58">
+      <c r="H73" s="21">
         <f t="shared" si="33"/>
         <v>14960</v>
       </c>
-      <c r="I73" s="58">
+      <c r="I73" s="21">
         <f t="shared" si="34"/>
         <v>43864.178781122231</v>
       </c>
-      <c r="J73" s="58">
+      <c r="J73" s="21">
         <f t="shared" si="35"/>
         <v>63864.178781122231</v>
       </c>
-      <c r="K73" s="58">
+      <c r="K73" s="21">
         <f t="shared" si="37"/>
         <v>2035.5594348357699</v>
       </c>
-      <c r="L73" s="58">
+      <c r="L73" s="21">
         <f t="shared" si="38"/>
         <v>2580.245810654249</v>
       </c>
-      <c r="M73" s="58">
+      <c r="M73" s="21">
         <f t="shared" si="36"/>
         <v>-17964.178781122231</v>
       </c>
-      <c r="N73" s="56" t="str">
+      <c r="N73" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O73" s="70">
+      <c r="O73" s="26">
         <f t="shared" si="40"/>
         <v>16.5</v>
       </c>
-      <c r="P73" s="58">
+      <c r="P73" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="74" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B74" s="41">
+      <c r="B74" s="20">
         <v>18</v>
       </c>
-      <c r="C74" s="43">
+      <c r="C74" s="11">
         <f t="shared" si="28"/>
         <v>1012.9676892512279</v>
       </c>
-      <c r="D74" s="43">
+      <c r="D74" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E74" s="43">
+      <c r="E74" s="11">
         <f t="shared" si="30"/>
         <v>292.96768925122785</v>
       </c>
-      <c r="F74" s="53">
+      <c r="F74" s="18">
         <f t="shared" si="31"/>
         <v>0.20344978420224155</v>
       </c>
-      <c r="G74" s="58">
+      <c r="G74" s="21">
         <f t="shared" si="32"/>
         <v>30086.244605056039</v>
       </c>
-      <c r="H74" s="58">
+      <c r="H74" s="21">
         <f t="shared" si="33"/>
         <v>15840</v>
       </c>
-      <c r="I74" s="58">
+      <c r="I74" s="21">
         <f t="shared" si="34"/>
         <v>45926.244605056039</v>
       </c>
-      <c r="J74" s="58">
+      <c r="J74" s="21">
         <f t="shared" si="35"/>
         <v>65926.244605056039</v>
       </c>
-      <c r="K74" s="58">
+      <c r="K74" s="21">
         <f t="shared" si="37"/>
         <v>2062.0658239338081</v>
       </c>
-      <c r="L74" s="58">
+      <c r="L74" s="21">
         <f t="shared" si="38"/>
         <v>2551.4580336142244</v>
       </c>
-      <c r="M74" s="58">
+      <c r="M74" s="21">
         <f t="shared" si="36"/>
         <v>-17326.244605056039</v>
       </c>
-      <c r="N74" s="56" t="str">
+      <c r="N74" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O74" s="70">
+      <c r="O74" s="26">
         <f t="shared" si="40"/>
         <v>17.5</v>
       </c>
-      <c r="P74" s="58">
+      <c r="P74" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="75" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B75" s="41">
+      <c r="B75" s="20">
         <v>19</v>
       </c>
-      <c r="C75" s="43">
+      <c r="C75" s="11">
         <f t="shared" si="28"/>
         <v>1082.6092178872495</v>
       </c>
-      <c r="D75" s="43">
+      <c r="D75" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E75" s="43">
+      <c r="E75" s="11">
         <f t="shared" si="30"/>
         <v>362.60921788724954</v>
       </c>
-      <c r="F75" s="53">
+      <c r="F75" s="18">
         <f t="shared" si="31"/>
         <v>0.25181195686614549</v>
       </c>
-      <c r="G75" s="58">
+      <c r="G75" s="21">
         <f t="shared" si="32"/>
         <v>31295.298921653637</v>
       </c>
-      <c r="H75" s="58">
+      <c r="H75" s="21">
         <f t="shared" si="33"/>
         <v>16720</v>
       </c>
-      <c r="I75" s="58">
+      <c r="I75" s="21">
         <f t="shared" si="34"/>
         <v>48015.298921653637</v>
       </c>
-      <c r="J75" s="58">
+      <c r="J75" s="21">
         <f t="shared" si="35"/>
         <v>68015.298921653637</v>
       </c>
-      <c r="K75" s="58">
+      <c r="K75" s="21">
         <f t="shared" si="37"/>
         <v>2089.0543165975978</v>
       </c>
-      <c r="L75" s="58">
+      <c r="L75" s="21">
         <f t="shared" si="38"/>
         <v>2527.1209958765071</v>
       </c>
-      <c r="M75" s="58">
+      <c r="M75" s="21">
         <f t="shared" si="36"/>
         <v>-16715.298921653637</v>
       </c>
-      <c r="N75" s="56" t="str">
+      <c r="N75" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O75" s="70">
+      <c r="O75" s="26">
         <f t="shared" si="40"/>
         <v>18.5</v>
       </c>
-      <c r="P75" s="58">
+      <c r="P75" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="76" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B76" s="41">
+      <c r="B76" s="20">
         <v>20</v>
       </c>
-      <c r="C76" s="43">
+      <c r="C76" s="11">
         <f t="shared" si="28"/>
         <v>1153.8335085377266</v>
       </c>
-      <c r="D76" s="43">
+      <c r="D76" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E76" s="43">
+      <c r="E76" s="11">
         <f t="shared" si="30"/>
         <v>433.83350853772663</v>
       </c>
-      <c r="F76" s="53">
+      <c r="F76" s="18">
         <f t="shared" si="31"/>
         <v>0.30127326981786573</v>
       </c>
-      <c r="G76" s="58">
+      <c r="G76" s="21">
         <f t="shared" si="32"/>
         <v>32531.831745446641</v>
       </c>
-      <c r="H76" s="58">
+      <c r="H76" s="21">
         <f t="shared" si="33"/>
         <v>17600</v>
       </c>
-      <c r="I76" s="58">
+      <c r="I76" s="21">
         <f t="shared" si="34"/>
         <v>50131.831745446645</v>
       </c>
-      <c r="J76" s="58">
+      <c r="J76" s="21">
         <f t="shared" si="35"/>
         <v>70131.831745446645</v>
       </c>
-      <c r="K76" s="58">
+      <c r="K76" s="21">
         <f t="shared" si="37"/>
         <v>2116.532823793008</v>
       </c>
-      <c r="L76" s="58">
+      <c r="L76" s="21">
         <f t="shared" si="38"/>
         <v>2506.5915872723322</v>
       </c>
-      <c r="M76" s="58">
+      <c r="M76" s="21">
         <f t="shared" si="36"/>
         <v>-16131.831745446645</v>
       </c>
-      <c r="N76" s="56" t="str">
+      <c r="N76" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O76" s="70">
+      <c r="O76" s="26">
         <f t="shared" si="40"/>
         <v>19.5</v>
       </c>
-      <c r="P76" s="58">
+      <c r="P76" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="77" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B77" s="41">
+      <c r="B77" s="20">
         <v>21</v>
       </c>
-      <c r="C77" s="43">
+      <c r="C77" s="11">
         <f t="shared" si="28"/>
         <v>1226.6692487641703</v>
       </c>
-      <c r="D77" s="43">
+      <c r="D77" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E77" s="43">
+      <c r="E77" s="11">
         <f t="shared" si="30"/>
         <v>506.66924876417033</v>
       </c>
-      <c r="F77" s="53">
+      <c r="F77" s="18">
         <f t="shared" si="31"/>
         <v>0.35185364497511828</v>
       </c>
-      <c r="G77" s="58">
+      <c r="G77" s="21">
         <f t="shared" si="32"/>
         <v>33796.341124377956</v>
       </c>
-      <c r="H77" s="58">
+      <c r="H77" s="21">
         <f t="shared" si="33"/>
         <v>18480</v>
       </c>
-      <c r="I77" s="58">
+      <c r="I77" s="21">
         <f t="shared" si="34"/>
         <v>52276.341124377956</v>
       </c>
-      <c r="J77" s="58">
+      <c r="J77" s="21">
         <f t="shared" si="35"/>
         <v>72276.341124377956</v>
       </c>
-      <c r="K77" s="58">
+      <c r="K77" s="21">
         <f t="shared" si="37"/>
         <v>2144.5093789313105</v>
       </c>
-      <c r="L77" s="58">
+      <c r="L77" s="21">
         <f t="shared" si="38"/>
         <v>2489.3495773513314</v>
       </c>
-      <c r="M77" s="58">
+      <c r="M77" s="21">
         <f t="shared" si="36"/>
         <v>-15576.341124377956</v>
       </c>
-      <c r="N77" s="56" t="str">
+      <c r="N77" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O77" s="70">
+      <c r="O77" s="26">
         <f t="shared" si="40"/>
         <v>20.5</v>
       </c>
-      <c r="P77" s="58">
+      <c r="P77" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="78" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B78" s="41">
+      <c r="B78" s="20">
         <v>22</v>
       </c>
-      <c r="C78" s="43">
+      <c r="C78" s="11">
         <f t="shared" si="28"/>
         <v>1301.1455960105666</v>
       </c>
-      <c r="D78" s="43">
+      <c r="D78" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E78" s="43">
+      <c r="E78" s="11">
         <f t="shared" si="30"/>
         <v>581.14559601056658</v>
       </c>
-      <c r="F78" s="53">
+      <c r="F78" s="18">
         <f t="shared" si="31"/>
         <v>0.40357333056289346</v>
       </c>
-      <c r="G78" s="58">
+      <c r="G78" s="21">
         <f t="shared" si="32"/>
         <v>35089.333264072338</v>
       </c>
-      <c r="H78" s="58">
+      <c r="H78" s="21">
         <f t="shared" si="33"/>
         <v>19360</v>
       </c>
-      <c r="I78" s="58">
+      <c r="I78" s="21">
         <f t="shared" si="34"/>
         <v>54449.333264072338</v>
       </c>
-      <c r="J78" s="58">
+      <c r="J78" s="21">
         <f t="shared" si="35"/>
         <v>74449.333264072338</v>
       </c>
-      <c r="K78" s="58">
+      <c r="K78" s="21">
         <f t="shared" si="37"/>
         <v>2172.9921396943828</v>
       </c>
-      <c r="L78" s="58">
+      <c r="L78" s="21">
         <f t="shared" si="38"/>
         <v>2474.9696938214697</v>
       </c>
-      <c r="M78" s="58">
+      <c r="M78" s="21">
         <f t="shared" si="36"/>
         <v>-15049.333264072338</v>
       </c>
-      <c r="N78" s="56" t="str">
+      <c r="N78" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O78" s="70">
+      <c r="O78" s="26">
         <f t="shared" si="40"/>
         <v>21.5</v>
       </c>
-      <c r="P78" s="58">
+      <c r="P78" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="79" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B79" s="41">
+      <c r="B79" s="20">
         <v>23</v>
       </c>
-      <c r="C79" s="43">
+      <c r="C79" s="11">
         <f t="shared" si="28"/>
         <v>1377.292184868003</v>
       </c>
-      <c r="D79" s="43">
+      <c r="D79" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E79" s="43">
+      <c r="E79" s="11">
         <f t="shared" si="30"/>
         <v>657.29218486800301</v>
       </c>
-      <c r="F79" s="53">
+      <c r="F79" s="18">
         <f t="shared" si="31"/>
         <v>0.45645290615833545</v>
       </c>
-      <c r="G79" s="58">
+      <c r="G79" s="21">
         <f t="shared" si="32"/>
         <v>36411.322653958385</v>
       </c>
-      <c r="H79" s="58">
+      <c r="H79" s="21">
         <f t="shared" si="33"/>
         <v>20240</v>
       </c>
-      <c r="I79" s="58">
+      <c r="I79" s="21">
         <f t="shared" si="34"/>
         <v>56651.322653958385</v>
       </c>
-      <c r="J79" s="58">
+      <c r="J79" s="21">
         <f t="shared" si="35"/>
         <v>76651.322653958385</v>
       </c>
-      <c r="K79" s="58">
+      <c r="K79" s="21">
         <f t="shared" si="37"/>
         <v>2201.9893898860464</v>
       </c>
-      <c r="L79" s="58">
+      <c r="L79" s="21">
         <f t="shared" si="38"/>
         <v>2463.1009849547122</v>
       </c>
-      <c r="M79" s="58">
+      <c r="M79" s="21">
         <f t="shared" si="36"/>
         <v>-14551.322653958385</v>
       </c>
-      <c r="N79" s="56" t="str">
+      <c r="N79" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O79" s="70">
+      <c r="O79" s="26">
         <f t="shared" si="40"/>
         <v>22.5</v>
       </c>
-      <c r="P79" s="58">
+      <c r="P79" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="80" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B80" s="41">
+      <c r="B80" s="20">
         <v>24</v>
       </c>
-      <c r="C80" s="43">
+      <c r="C80" s="11">
         <f t="shared" si="28"/>
         <v>1455.1391344474989</v>
       </c>
-      <c r="D80" s="43">
+      <c r="D80" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E80" s="43">
+      <c r="E80" s="11">
         <f t="shared" si="30"/>
         <v>735.13913444749892</v>
       </c>
-      <c r="F80" s="53">
+      <c r="F80" s="18">
         <f t="shared" si="31"/>
         <v>0.51051328781076311</v>
       </c>
-      <c r="G80" s="58">
+      <c r="G80" s="21">
         <f t="shared" si="32"/>
         <v>37762.832195269075</v>
       </c>
-      <c r="H80" s="58">
+      <c r="H80" s="21">
         <f t="shared" si="33"/>
         <v>21120</v>
       </c>
-      <c r="I80" s="58">
+      <c r="I80" s="21">
         <f t="shared" si="34"/>
         <v>58882.832195269075</v>
       </c>
-      <c r="J80" s="58">
+      <c r="J80" s="21">
         <f t="shared" si="35"/>
         <v>78882.832195269075</v>
       </c>
-      <c r="K80" s="58">
+      <c r="K80" s="21">
         <f t="shared" si="37"/>
         <v>2231.5095413106901</v>
       </c>
-      <c r="L80" s="58">
+      <c r="L80" s="21">
         <f t="shared" si="38"/>
         <v>2453.4513414695448</v>
       </c>
-      <c r="M80" s="58">
+      <c r="M80" s="21">
         <f t="shared" si="36"/>
         <v>-14082.832195269075</v>
       </c>
-      <c r="N80" s="56" t="str">
+      <c r="N80" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O80" s="70">
+      <c r="O80" s="26">
         <f t="shared" si="40"/>
         <v>23.5</v>
       </c>
-      <c r="P80" s="58">
+      <c r="P80" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="81" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B81" s="41">
+      <c r="B81" s="20">
         <v>25</v>
       </c>
-      <c r="C81" s="43">
+      <c r="C81" s="11">
         <f t="shared" si="28"/>
         <v>1534.7170558625965</v>
       </c>
-      <c r="D81" s="43">
+      <c r="D81" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E81" s="43">
+      <c r="E81" s="11">
         <f t="shared" si="30"/>
         <v>814.71705586259645</v>
       </c>
-      <c r="F81" s="53">
+      <c r="F81" s="18">
         <f t="shared" si="31"/>
         <v>0.56577573323791419</v>
       </c>
-      <c r="G81" s="58">
+      <c r="G81" s="21">
         <f t="shared" si="32"/>
         <v>39144.393330947853</v>
       </c>
-      <c r="H81" s="58">
+      <c r="H81" s="21">
         <f t="shared" si="33"/>
         <v>22000</v>
       </c>
-      <c r="I81" s="58">
+      <c r="I81" s="21">
         <f t="shared" si="34"/>
         <v>61144.393330947853</v>
       </c>
-      <c r="J81" s="58">
+      <c r="J81" s="21">
         <f t="shared" si="35"/>
         <v>81144.393330947845</v>
       </c>
-      <c r="K81" s="58">
+      <c r="K81" s="21">
         <f t="shared" si="37"/>
         <v>2261.5611356787704</v>
       </c>
-      <c r="L81" s="58">
+      <c r="L81" s="21">
         <f t="shared" si="38"/>
         <v>2445.7757332379142</v>
       </c>
-      <c r="M81" s="58">
+      <c r="M81" s="21">
         <f t="shared" si="36"/>
         <v>-13644.393330947845</v>
       </c>
-      <c r="N81" s="56" t="str">
+      <c r="N81" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O81" s="70">
+      <c r="O81" s="26">
         <f t="shared" si="40"/>
         <v>24.5</v>
       </c>
-      <c r="P81" s="58">
+      <c r="P81" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="82" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B82" s="41">
+      <c r="B82" s="20">
         <v>26</v>
       </c>
-      <c r="C82" s="43">
+      <c r="C82" s="11">
         <f t="shared" si="28"/>
         <v>1616.0570598233144</v>
       </c>
-      <c r="D82" s="43">
+      <c r="D82" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E82" s="43">
+      <c r="E82" s="11">
         <f t="shared" si="30"/>
         <v>896.05705982331438</v>
       </c>
-      <c r="F82" s="53">
+      <c r="F82" s="18">
         <f t="shared" si="31"/>
         <v>0.62226184709952392</v>
       </c>
-      <c r="G82" s="58">
+      <c r="G82" s="21">
         <f t="shared" si="32"/>
         <v>40556.546177488097</v>
       </c>
-      <c r="H82" s="58">
+      <c r="H82" s="21">
         <f t="shared" si="33"/>
         <v>22880</v>
       </c>
-      <c r="I82" s="58">
+      <c r="I82" s="21">
         <f t="shared" si="34"/>
         <v>63436.546177488097</v>
       </c>
-      <c r="J82" s="58">
+      <c r="J82" s="21">
         <f t="shared" si="35"/>
         <v>83436.546177488097</v>
       </c>
-      <c r="K82" s="58">
+      <c r="K82" s="21">
         <f t="shared" si="37"/>
         <v>2292.1528465402516</v>
       </c>
-      <c r="L82" s="58">
+      <c r="L82" s="21">
         <f t="shared" si="38"/>
         <v>2439.8671606726193</v>
       </c>
-      <c r="M82" s="58">
+      <c r="M82" s="21">
         <f t="shared" si="36"/>
         <v>-13236.546177488097</v>
       </c>
-      <c r="N82" s="56" t="str">
+      <c r="N82" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O82" s="70">
+      <c r="O82" s="26">
         <f t="shared" si="40"/>
         <v>25.5</v>
       </c>
-      <c r="P82" s="58">
+      <c r="P82" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="83" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B83" s="41">
+      <c r="B83" s="20">
         <v>27</v>
       </c>
-      <c r="C83" s="43">
+      <c r="C83" s="11">
         <f t="shared" si="28"/>
         <v>1699.1907643430709</v>
       </c>
-      <c r="D83" s="43">
+      <c r="D83" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E83" s="43">
+      <c r="E83" s="11">
         <f t="shared" si="30"/>
         <v>979.1907643430709</v>
       </c>
-      <c r="F83" s="53">
+      <c r="F83" s="18">
         <f t="shared" si="31"/>
         <v>0.67999358634935481</v>
       </c>
-      <c r="G83" s="58">
+      <c r="G83" s="21">
         <f t="shared" si="32"/>
         <v>41999.839658733865</v>
       </c>
-      <c r="H83" s="58">
+      <c r="H83" s="21">
         <f t="shared" si="33"/>
         <v>23760</v>
       </c>
-      <c r="I83" s="58">
+      <c r="I83" s="21">
         <f t="shared" si="34"/>
         <v>65759.839658733865</v>
       </c>
-      <c r="J83" s="58">
+      <c r="J83" s="21">
         <f t="shared" si="35"/>
         <v>85759.839658733865</v>
       </c>
-      <c r="K83" s="58">
+      <c r="K83" s="21">
         <f t="shared" si="37"/>
         <v>2323.2934812457679</v>
       </c>
-      <c r="L83" s="58">
+      <c r="L83" s="21">
         <f t="shared" si="38"/>
         <v>2435.549616990143</v>
       </c>
-      <c r="M83" s="58">
+      <c r="M83" s="21">
         <f t="shared" si="36"/>
         <v>-12859.839658733865</v>
       </c>
-      <c r="N83" s="56" t="str">
+      <c r="N83" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O83" s="70">
+      <c r="O83" s="26">
         <f t="shared" si="40"/>
         <v>26.5</v>
       </c>
-      <c r="P83" s="58">
+      <c r="P83" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="84" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B84" s="41">
+      <c r="B84" s="20">
         <v>28</v>
       </c>
-      <c r="C84" s="43">
+      <c r="C84" s="11">
         <f t="shared" si="28"/>
         <v>1784.1503025602246</v>
       </c>
-      <c r="D84" s="43">
+      <c r="D84" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E84" s="43">
+      <c r="E84" s="11">
         <f t="shared" si="30"/>
         <v>1064.1503025602246</v>
       </c>
-      <c r="F84" s="53">
+      <c r="F84" s="18">
         <f t="shared" si="31"/>
         <v>0.73899326566682266</v>
       </c>
-      <c r="G84" s="58">
+      <c r="G84" s="21">
         <f t="shared" si="32"/>
         <v>43474.831641670564</v>
       </c>
-      <c r="H84" s="58">
+      <c r="H84" s="21">
         <f t="shared" si="33"/>
         <v>24640</v>
       </c>
-      <c r="I84" s="58">
+      <c r="I84" s="21">
         <f t="shared" si="34"/>
         <v>68114.831641670564</v>
       </c>
-      <c r="J84" s="58">
+      <c r="J84" s="21">
         <f t="shared" si="35"/>
         <v>88114.831641670564</v>
       </c>
-      <c r="K84" s="58">
+      <c r="K84" s="21">
         <f t="shared" si="37"/>
         <v>2354.9919829366991</v>
       </c>
-      <c r="L84" s="58">
+      <c r="L84" s="21">
         <f t="shared" si="38"/>
         <v>2432.6725586310918</v>
       </c>
-      <c r="M84" s="58">
+      <c r="M84" s="21">
         <f t="shared" si="36"/>
         <v>-12514.831641670564</v>
       </c>
-      <c r="N84" s="56" t="str">
+      <c r="N84" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O84" s="70">
+      <c r="O84" s="26">
         <f t="shared" si="40"/>
         <v>27.5</v>
       </c>
-      <c r="P84" s="58">
+      <c r="P84" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="85" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B85" s="41">
+      <c r="B85" s="20">
         <v>29</v>
       </c>
-      <c r="C85" s="43">
+      <c r="C85" s="11">
         <f t="shared" si="28"/>
         <v>1870.9683306758782</v>
       </c>
-      <c r="D85" s="43">
+      <c r="D85" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E85" s="43">
+      <c r="E85" s="11">
         <f t="shared" si="30"/>
         <v>1150.9683306758782</v>
       </c>
-      <c r="F85" s="53">
+      <c r="F85" s="18">
         <f t="shared" si="31"/>
         <v>0.79928356296935987</v>
       </c>
-      <c r="G85" s="58">
+      <c r="G85" s="21">
         <f t="shared" si="32"/>
         <v>44982.089074233998</v>
       </c>
-      <c r="H85" s="58">
+      <c r="H85" s="21">
         <f t="shared" si="33"/>
         <v>25520</v>
       </c>
-      <c r="I85" s="58">
+      <c r="I85" s="21">
         <f t="shared" si="34"/>
         <v>70502.089074233998</v>
       </c>
-      <c r="J85" s="58">
+      <c r="J85" s="21">
         <f t="shared" si="35"/>
         <v>90502.089074233998</v>
       </c>
-      <c r="K85" s="58">
+      <c r="K85" s="21">
         <f t="shared" si="37"/>
         <v>2387.2574325634341</v>
       </c>
-      <c r="L85" s="58">
+      <c r="L85" s="21">
         <f t="shared" si="38"/>
         <v>2431.1065198011725</v>
       </c>
-      <c r="M85" s="58">
+      <c r="M85" s="21">
         <f t="shared" si="36"/>
         <v>-12202.089074233998</v>
       </c>
-      <c r="N85" s="56" t="str">
+      <c r="N85" s="8" t="str">
         <f t="shared" si="39"/>
         <v/>
       </c>
-      <c r="O85" s="70">
+      <c r="O85" s="26">
         <f t="shared" si="40"/>
         <v>28.5</v>
       </c>
-      <c r="P85" s="58">
+      <c r="P85" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>
     </row>
     <row r="86" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B86" s="41">
+      <c r="B86" s="20">
         <v>30</v>
       </c>
-      <c r="C86" s="43">
+      <c r="C86" s="11">
         <f t="shared" si="28"/>
         <v>1959.6780360096488</v>
       </c>
-      <c r="D86" s="43">
+      <c r="D86" s="11">
         <f t="shared" si="29"/>
         <v>720</v>
       </c>
-      <c r="E86" s="43">
+      <c r="E86" s="11">
         <f t="shared" si="30"/>
         <v>1239.6780360096488</v>
       </c>
-      <c r="F86" s="53">
+      <c r="F86" s="18">
         <f t="shared" si="31"/>
         <v>0.86088752500670063</v>
       </c>
-      <c r="G86" s="58">
+      <c r="G86" s="21">
         <f t="shared" si="32"/>
         <v>46522.188125167515</v>
       </c>
-      <c r="H86" s="58">
+      <c r="H86" s="21">
         <f t="shared" si="33"/>
         <v>26400</v>
       </c>
-      <c r="I86" s="58">
+      <c r="I86" s="21">
         <f t="shared" si="34"/>
         <v>72922.188125167508</v>
       </c>
-      <c r="J86" s="58">
+      <c r="J86" s="21">
         <f t="shared" si="35"/>
         <v>92922.188125167508</v>
       </c>
-      <c r="K86" s="58">
+      <c r="K86" s="21">
         <f t="shared" si="37"/>
         <v>2420.0990509335097</v>
       </c>
-      <c r="L86" s="58">
+      <c r="L86" s="21">
         <f t="shared" si="38"/>
         <v>2430.7396041722504</v>
       </c>
-      <c r="M86" s="58">
+      <c r="M86" s="21">
         <f t="shared" si="36"/>
         <v>-11922.188125167508</v>
       </c>
-      <c r="N86" s="69" t="str">
+      <c r="N86" s="8" t="str">
         <f>IF(F86&gt;temp_max,"INFEASIBLE","")</f>
         <v/>
       </c>
-      <c r="O86" s="70">
+      <c r="O86" s="26">
         <f t="shared" si="40"/>
         <v>29.5</v>
       </c>
-      <c r="P86" s="58">
+      <c r="P86" s="21">
         <f t="shared" si="41"/>
         <v>2700</v>
       </c>

--- a/courses/Micro-And-Macro-Economics/projects/perfect-competition-marginal-costs/farm-profit-optimizer-key.xlsx
+++ b/courses/Micro-And-Macro-Economics/projects/perfect-competition-marginal-costs/farm-profit-optimizer-key.xlsx
@@ -135,7 +135,7 @@
     <t>HOW TO USE</t>
   </si>
   <si>
-    <t>1. Read the assumptions on the Model sheet. Blue cells are inputs you may change; black cells are formulas — do not overtype them.</t>
+    <t>1. Read the assumptions on the Model sheet. The tan cells are the inputs you may change; everything else is a formula — do not overtype it.</t>
   </si>
   <si>
     <t>2. Enter a planting plan in the DECISION cells (beds of each crop). Watch the constraint checks: total beds &lt;= 64, temp workers &lt;= 4, each crop &lt;= its max.</t>
@@ -168,13 +168,13 @@
     <t>COLOR KEY</t>
   </si>
   <si>
-    <t>Blue text = input you can change</t>
-  </si>
-  <si>
-    <t>Black text = formula (do not overtype)</t>
-  </si>
-  <si>
-    <t>Yellow fill = decision cells Solver changes</t>
+    <t>Tan fill = input — hardcoded. A number typed in, not calculated. These are the cells you may change.</t>
+  </si>
+  <si>
+    <t>Blue text = formula — calculated. Never type over it. The plain black formulas are calculated too.</t>
+  </si>
+  <si>
+    <t>Yellow fill = key assumption — the decision cells Solver changes</t>
   </si>
   <si>
     <t>FIXES vs v5 (instructor reference)</t>
@@ -186,7 +186,7 @@
     <t>- Temp-labor cap previously compared hours to 1,440 instead of 4 workers; now temp_needed &lt;= temp_max is an explicit checked constraint.</t>
   </si>
   <si>
-    <t>- Wages were hardcoded (=50000/...) inside formulas; salaries are now blue input cells.</t>
+    <t>- Wages were hardcoded (=50000/...) inside formulas; salaries are now separate tan input cells.</t>
   </si>
   <si>
     <t>- Named-range typos fixed (fert_carrotrs, labour_hrs, 'Tomotoes', 'Mesculun').</t>
@@ -501,7 +501,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <charset val="1"/>
     </font>
@@ -538,7 +538,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -593,6 +593,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -606,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -658,6 +664,16 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3208,12 +3224,12 @@
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="39" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="45" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3223,7 +3239,7 @@
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="46" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3297,7 +3313,7 @@
       <c r="B5" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="40">
         <v>36</v>
       </c>
     </row>
@@ -3305,7 +3321,7 @@
       <c r="B6" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6" s="41">
         <v>20000</v>
       </c>
     </row>
@@ -3313,7 +3329,7 @@
       <c r="B7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="40">
         <v>40</v>
       </c>
     </row>
@@ -3347,10 +3363,10 @@
       <c r="B11" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="10">
+      <c r="C11" s="41">
         <v>50000</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="42">
         <v>0.5</v>
       </c>
       <c r="E11" s="14">
@@ -3366,10 +3382,10 @@
       <c r="B12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="41">
         <v>25000</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="42">
         <v>1</v>
       </c>
       <c r="E12" s="14">
@@ -3455,19 +3471,19 @@
       <c r="B20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="40">
         <v>20</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="41">
         <v>8800</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="43">
         <v>2.5</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="41">
         <v>880</v>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="44">
         <v>0.1</v>
       </c>
       <c r="H20" s="8" t="s">
@@ -3478,20 +3494,20 @@
       <c r="B21" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="40">
         <v>20</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D21" s="41">
         <v>2094</v>
       </c>
       <c r="E21" s="18">
         <f>E20/3</f>
         <v>0.83333333333333337</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="41">
         <v>440</v>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="44">
         <v>2.5000000000000001E-2</v>
       </c>
     </row>
@@ -3499,20 +3515,20 @@
       <c r="B22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="40">
         <v>30</v>
       </c>
-      <c r="D22" s="10">
+      <c r="D22" s="41">
         <v>2700</v>
       </c>
       <c r="E22" s="18">
         <f>E20/2</f>
         <v>1.25</v>
       </c>
-      <c r="F22" s="10">
+      <c r="F22" s="41">
         <v>880</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="44">
         <v>1.2500000000000001E-2</v>
       </c>
     </row>
